--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -2568,7 +2568,7 @@
         <v>136457415</v>
       </c>
       <c r="B19" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>136489706</v>
       </c>
       <c r="B44" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>136489707</v>
       </c>
       <c r="B45" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -2568,7 +2568,7 @@
         <v>136457415</v>
       </c>
       <c r="B19" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>136489706</v>
       </c>
       <c r="B44" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>136489707</v>
       </c>
       <c r="B45" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -2568,7 +2568,7 @@
         <v>136457415</v>
       </c>
       <c r="B19" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>136489706</v>
       </c>
       <c r="B44" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>136489707</v>
       </c>
       <c r="B45" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ98"/>
+  <dimension ref="A1:AZ100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2016,51 +2016,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119096505</v>
+        <v>136854171</v>
       </c>
       <c r="B14" t="n">
-        <v>91394</v>
+        <v>91117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2051</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Unnån, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480846</v>
+        <v>480987</v>
       </c>
       <c r="R14" t="n">
-        <v>6787516</v>
+        <v>6787699</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,22 +2081,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,39 +2095,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>I brant slänt på isälvssediment, mest gran i närheten, tall längre bort.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119096505</t>
+          <t>https://artportalen.se/Sighting/136854171</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112922790</v>
+        <v>119096505</v>
       </c>
       <c r="B15" t="n">
-        <v>93213</v>
+        <v>91394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,47 +2129,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480742</v>
+        <v>480846</v>
       </c>
       <c r="R15" t="n">
-        <v>6787676</v>
+        <v>6787516</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2212,22 +2186,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,30 +2210,36 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>I brant slänt på isälvssediment, mest gran i närheten, tall längre bort.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922790</t>
+          <t>https://artportalen.se/Sighting/119096505</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121972897</v>
+        <v>112922790</v>
       </c>
       <c r="B16" t="n">
         <v>93213</v>
@@ -2287,20 +2267,30 @@
           <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481022</v>
+        <v>480742</v>
       </c>
       <c r="R16" t="n">
-        <v>6787739</v>
+        <v>6787676</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,12 +2314,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,24 +2344,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972897</t>
+          <t>https://artportalen.se/Sighting/112922790</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121972898</v>
+        <v>121972897</v>
       </c>
       <c r="B17" t="n">
         <v>93213</v>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480829</v>
+        <v>481022</v>
       </c>
       <c r="R17" t="n">
-        <v>6787731</v>
+        <v>6787739</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,13 +2457,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972898</t>
+          <t>https://artportalen.se/Sighting/121972897</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121972901</v>
+        <v>121972898</v>
       </c>
       <c r="B18" t="n">
         <v>93213</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480745</v>
+        <v>480829</v>
       </c>
       <c r="R18" t="n">
-        <v>6787692</v>
+        <v>6787731</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2559,16 +2559,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972901</t>
+          <t>https://artportalen.se/Sighting/121972898</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136457415</v>
+        <v>121972901</v>
       </c>
       <c r="B19" t="n">
-        <v>93425</v>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2596,14 +2596,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, SV Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480744</v>
+        <v>480745</v>
       </c>
       <c r="R19" t="n">
-        <v>6787688</v>
+        <v>6787692</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2630,22 +2630,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,62 +2650,62 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136457415</t>
+          <t>https://artportalen.se/Sighting/121972901</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121972912</v>
+        <v>136457415</v>
       </c>
       <c r="B20" t="n">
-        <v>91962</v>
+        <v>93427</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>SV Ekentjärn, SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480966</v>
+        <v>480744</v>
       </c>
       <c r="R20" t="n">
-        <v>6787791</v>
+        <v>6787688</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2742,12 +2732,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,27 +2762,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972912</t>
+          <t>https://artportalen.se/Sighting/136457415</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121972884</v>
+        <v>121972912</v>
       </c>
       <c r="B21" t="n">
-        <v>87325</v>
+        <v>91962</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,37 +2790,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3690</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480986</v>
+        <v>480966</v>
       </c>
       <c r="R21" t="n">
-        <v>6787836</v>
+        <v>6787791</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,11 +2852,6 @@
           <t>2024-09-03</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2883,16 +2875,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972884</t>
+          <t>https://artportalen.se/Sighting/121972912</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119096496</v>
+        <v>121972884</v>
       </c>
       <c r="B22" t="n">
-        <v>93189</v>
+        <v>87325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2900,21 +2892,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2923,17 +2915,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Unnån, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480846</v>
+        <v>480986</v>
       </c>
       <c r="R22" t="n">
-        <v>6787516</v>
+        <v>6787836</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2957,12 +2949,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2971,7 +2968,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2989,13 +2985,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119096496</t>
+          <t>https://artportalen.se/Sighting/121972884</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119565699</v>
+        <v>119096496</v>
       </c>
       <c r="B23" t="n">
         <v>93189</v>
@@ -3023,31 +3019,23 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480853</v>
+        <v>480846</v>
       </c>
       <c r="R23" t="n">
         <v>6787516</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3071,22 +3059,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,24 +3080,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565699</t>
+          <t>https://artportalen.se/Sighting/119096496</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119565742</v>
+        <v>119565699</v>
       </c>
       <c r="B24" t="n">
         <v>93189</v>
@@ -3149,7 +3127,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3161,14 +3139,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Siljansleden, Siljansleden, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480845</v>
+        <v>480853</v>
       </c>
       <c r="R24" t="n">
-        <v>6787511</v>
+        <v>6787516</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3200,7 +3178,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3210,7 +3188,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,13 +3215,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565742</t>
+          <t>https://artportalen.se/Sighting/119565699</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119566308</v>
+        <v>119565742</v>
       </c>
       <c r="B25" t="n">
         <v>93189</v>
@@ -3273,7 +3251,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3285,14 +3263,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Siljansleden, Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480816</v>
+        <v>480845</v>
       </c>
       <c r="R25" t="n">
-        <v>6787542</v>
+        <v>6787511</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3324,7 +3302,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,7 +3312,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3361,13 +3339,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119566308</t>
+          <t>https://artportalen.se/Sighting/119565742</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119568829</v>
+        <v>119566308</v>
       </c>
       <c r="B26" t="n">
         <v>93189</v>
@@ -3397,25 +3375,29 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480735</v>
+        <v>480816</v>
       </c>
       <c r="R26" t="n">
-        <v>6787658</v>
+        <v>6787542</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3442,9 +3424,19 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,24 +3452,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568829</t>
+          <t>https://artportalen.se/Sighting/119566308</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121972911</v>
+        <v>119568829</v>
       </c>
       <c r="B27" t="n">
         <v>93189</v>
@@ -3505,20 +3497,27 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480843</v>
+        <v>480735</v>
       </c>
       <c r="R27" t="n">
-        <v>6787540</v>
+        <v>6787658</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3542,12 +3541,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3556,33 +3555,34 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972911</t>
+          <t>https://artportalen.se/Sighting/119568829</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112922923</v>
+        <v>121972911</v>
       </c>
       <c r="B28" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3590,38 +3590,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480772</v>
+        <v>480843</v>
       </c>
       <c r="R28" t="n">
-        <v>6787679</v>
+        <v>6787540</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3645,22 +3644,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3675,24 +3664,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922923</t>
+          <t>https://artportalen.se/Sighting/121972911</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112922930</v>
+        <v>112922923</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3720,16 +3709,7 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3737,13 +3717,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480779</v>
+        <v>480772</v>
       </c>
       <c r="R29" t="n">
-        <v>6787677</v>
+        <v>6787679</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3772,7 +3752,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3782,7 +3762,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3808,13 +3788,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922930</t>
+          <t>https://artportalen.se/Sighting/112922923</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112923242</v>
+        <v>112922930</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3844,7 +3824,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3859,13 +3839,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480760</v>
+        <v>480779</v>
       </c>
       <c r="R30" t="n">
-        <v>6787645</v>
+        <v>6787677</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3894,7 +3874,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3904,7 +3884,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,13 +3910,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923242</t>
+          <t>https://artportalen.se/Sighting/112922930</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112996027</v>
+        <v>112923242</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3966,7 +3946,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3975,17 +3955,16 @@
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480947</v>
+        <v>480760</v>
       </c>
       <c r="R31" t="n">
-        <v>6787809</v>
+        <v>6787645</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4012,12 +3991,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4026,31 +4015,30 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996027</t>
+          <t>https://artportalen.se/Sighting/112923242</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112996030</v>
+        <v>112996027</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -4080,7 +4068,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4096,10 +4084,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481005</v>
+        <v>480947</v>
       </c>
       <c r="R32" t="n">
-        <v>6787834</v>
+        <v>6787809</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4158,13 +4146,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996030</t>
+          <t>https://artportalen.se/Sighting/112996027</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119545661</v>
+        <v>112996030</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -4192,8 +4180,16 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4202,13 +4198,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481008</v>
+        <v>481005</v>
       </c>
       <c r="R33" t="n">
-        <v>6787840</v>
+        <v>6787834</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4232,17 +4228,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>rikligt, tiotals</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4258,24 +4249,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119545661</t>
+          <t>https://artportalen.se/Sighting/112996030</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120837852</v>
+        <v>119545661</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4303,16 +4294,8 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4321,13 +4304,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481001</v>
+        <v>481008</v>
       </c>
       <c r="R34" t="n">
-        <v>6787844</v>
+        <v>6787840</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4351,12 +4334,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>rikligt, tiotals</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4372,24 +4360,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120837852</t>
+          <t>https://artportalen.se/Sighting/119545661</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121972915</v>
+        <v>120837852</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4417,14 +4405,25 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480914</v>
+        <v>481001</v>
       </c>
       <c r="R35" t="n">
         <v>6787844</v>
@@ -4454,12 +4453,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4468,30 +4467,31 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972915</t>
+          <t>https://artportalen.se/Sighting/120837852</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121972916</v>
+        <v>121972915</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480915</v>
+        <v>480914</v>
       </c>
       <c r="R36" t="n">
-        <v>6787807</v>
+        <v>6787844</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4587,13 +4587,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972916</t>
+          <t>https://artportalen.se/Sighting/121972915</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121972917</v>
+        <v>121972916</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480797</v>
+        <v>480915</v>
       </c>
       <c r="R37" t="n">
-        <v>6787722</v>
+        <v>6787807</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4689,13 +4689,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972917</t>
+          <t>https://artportalen.se/Sighting/121972916</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121972918</v>
+        <v>121972917</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480812</v>
+        <v>480797</v>
       </c>
       <c r="R38" t="n">
-        <v>6787702</v>
+        <v>6787722</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4791,13 +4791,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972918</t>
+          <t>https://artportalen.se/Sighting/121972917</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121972919</v>
+        <v>121972918</v>
       </c>
       <c r="B39" t="n">
         <v>93197</v>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480773</v>
+        <v>480812</v>
       </c>
       <c r="R39" t="n">
-        <v>6787678</v>
+        <v>6787702</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4893,13 +4893,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972919</t>
+          <t>https://artportalen.se/Sighting/121972918</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121972920</v>
+        <v>121972919</v>
       </c>
       <c r="B40" t="n">
         <v>93197</v>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480994</v>
+        <v>480773</v>
       </c>
       <c r="R40" t="n">
-        <v>6787675</v>
+        <v>6787678</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4995,13 +4995,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972920</t>
+          <t>https://artportalen.se/Sighting/121972919</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121972921</v>
+        <v>121972920</v>
       </c>
       <c r="B41" t="n">
         <v>93197</v>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480761</v>
+        <v>480994</v>
       </c>
       <c r="R41" t="n">
-        <v>6787650</v>
+        <v>6787675</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5097,13 +5097,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972921</t>
+          <t>https://artportalen.se/Sighting/121972920</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121972922</v>
+        <v>121972921</v>
       </c>
       <c r="B42" t="n">
         <v>93197</v>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480796</v>
+        <v>480761</v>
       </c>
       <c r="R42" t="n">
-        <v>6787645</v>
+        <v>6787650</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5199,13 +5199,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972922</t>
+          <t>https://artportalen.se/Sighting/121972921</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127640071</v>
+        <v>121972922</v>
       </c>
       <c r="B43" t="n">
         <v>93197</v>
@@ -5236,14 +5236,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480961</v>
+        <v>480796</v>
       </c>
       <c r="R43" t="n">
-        <v>6787858</v>
+        <v>6787645</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5290,27 +5290,27 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alexander Singer, Andreas Öster, Cecilia Öster, Lina Lejonberg, Malte Lindberg</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127640071</t>
+          <t>https://artportalen.se/Sighting/121972922</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136489706</v>
+        <v>127640071</v>
       </c>
       <c r="B44" t="n">
-        <v>93409</v>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5338,17 +5338,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481015</v>
+        <v>480961</v>
       </c>
       <c r="R44" t="n">
-        <v>6787850</v>
+        <v>6787858</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5372,22 +5372,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5402,27 +5392,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+          <t>Alexander Singer, Andreas Öster, Cecilia Öster, Lina Lejonberg, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136489706</t>
+          <t>https://artportalen.se/Sighting/127640071</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136489707</v>
+        <v>136489706</v>
       </c>
       <c r="B45" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5454,13 +5444,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481006</v>
+        <v>481015</v>
       </c>
       <c r="R45" t="n">
-        <v>6787842</v>
+        <v>6787850</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5525,16 +5515,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136489707</t>
+          <t>https://artportalen.se/Sighting/136489706</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121972907</v>
+        <v>136489707</v>
       </c>
       <c r="B46" t="n">
-        <v>93209</v>
+        <v>93411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5542,21 +5532,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5566,13 +5556,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480936</v>
+        <v>481006</v>
       </c>
       <c r="R46" t="n">
-        <v>6787692</v>
+        <v>6787842</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5596,12 +5586,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5616,49 +5616,49 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972907</t>
+          <t>https://artportalen.se/Sighting/136489707</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112996025</v>
+        <v>121972907</v>
       </c>
       <c r="B47" t="n">
-        <v>91893</v>
+        <v>93209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4660</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480874</v>
+        <v>480936</v>
       </c>
       <c r="R47" t="n">
-        <v>6787479</v>
+        <v>6787692</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5698,12 +5698,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5718,72 +5718,65 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996025</t>
+          <t>https://artportalen.se/Sighting/121972907</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112996029</v>
+        <v>112996025</v>
       </c>
       <c r="B48" t="n">
-        <v>90522</v>
+        <v>91893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4962</v>
+        <v>4660</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481007</v>
+        <v>480874</v>
       </c>
       <c r="R48" t="n">
-        <v>6787835</v>
+        <v>6787479</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5838,16 +5831,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996029</t>
+          <t>https://artportalen.se/Sighting/112996025</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112914094</v>
+        <v>112996029</v>
       </c>
       <c r="B49" t="n">
-        <v>91930</v>
+        <v>90522</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5855,37 +5848,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>4962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480743</v>
+        <v>481007</v>
       </c>
       <c r="R49" t="n">
-        <v>6787694</v>
+        <v>6787835</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5912,12 +5909,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5926,34 +5923,33 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914094</t>
+          <t>https://artportalen.se/Sighting/112996029</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112923898</v>
+        <v>112914094</v>
       </c>
       <c r="B50" t="n">
-        <v>93223</v>
+        <v>91930</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5961,45 +5957,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480942</v>
+        <v>480743</v>
       </c>
       <c r="R50" t="n">
-        <v>6787720</v>
+        <v>6787694</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6026,22 +6014,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6057,27 +6035,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923898</t>
+          <t>https://artportalen.se/Sighting/112914094</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112996028</v>
+        <v>112923898</v>
       </c>
       <c r="B51" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6085,37 +6063,48 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480995</v>
+        <v>480942</v>
       </c>
       <c r="R51" t="n">
-        <v>6787829</v>
+        <v>6787720</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6139,12 +6128,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6153,71 +6152,69 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996028</t>
+          <t>https://artportalen.se/Sighting/112923898</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>96117407</v>
+        <v>112996028</v>
       </c>
       <c r="B52" t="n">
-        <v>79327</v>
+        <v>93235</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480781</v>
+        <v>480995</v>
       </c>
       <c r="R52" t="n">
-        <v>6787572</v>
+        <v>6787829</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6244,12 +6241,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6258,46 +6255,30 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96117407</t>
+          <t>https://artportalen.se/Sighting/112996028</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112914136</v>
+        <v>96117407</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -6331,14 +6312,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480780</v>
+        <v>480781</v>
       </c>
       <c r="R53" t="n">
-        <v>6787640</v>
+        <v>6787572</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6365,17 +6346,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6388,6 +6364,21 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
@@ -6402,13 +6393,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914136</t>
+          <t>https://artportalen.se/Sighting/96117407</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112923198</v>
+        <v>112914136</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6437,20 +6428,22 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480817</v>
+        <v>480780</v>
       </c>
       <c r="R54" t="n">
-        <v>6787576</v>
+        <v>6787640</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6474,27 +6467,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6503,30 +6486,31 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923198</t>
+          <t>https://artportalen.se/Sighting/112914136</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112923608</v>
+        <v>112923198</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6562,13 +6546,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480882</v>
+        <v>480817</v>
       </c>
       <c r="R55" t="n">
-        <v>6787809</v>
+        <v>6787576</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6597,7 +6581,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6607,7 +6591,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6633,13 +6622,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923608</t>
+          <t>https://artportalen.se/Sighting/112923198</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112924155</v>
+        <v>112923608</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6675,13 +6664,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480927</v>
+        <v>480882</v>
       </c>
       <c r="R56" t="n">
-        <v>6787699</v>
+        <v>6787809</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6710,7 +6699,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6720,7 +6709,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6746,13 +6735,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924155</t>
+          <t>https://artportalen.se/Sighting/112923608</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120747170</v>
+        <v>112924155</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6781,22 +6770,20 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480886</v>
+        <v>480927</v>
       </c>
       <c r="R57" t="n">
-        <v>6787539</v>
+        <v>6787699</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6820,17 +6807,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6839,31 +6831,30 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747170</t>
+          <t>https://artportalen.se/Sighting/112924155</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120747198</v>
+        <v>120747170</v>
       </c>
       <c r="B58" t="n">
         <v>79327</v>
@@ -6901,10 +6892,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480878</v>
+        <v>480886</v>
       </c>
       <c r="R58" t="n">
-        <v>6787512</v>
+        <v>6787539</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6968,13 +6959,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747198</t>
+          <t>https://artportalen.se/Sighting/120747170</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120747228</v>
+        <v>120747198</v>
       </c>
       <c r="B59" t="n">
         <v>79327</v>
@@ -7012,10 +7003,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480890</v>
+        <v>480878</v>
       </c>
       <c r="R59" t="n">
-        <v>6787571</v>
+        <v>6787512</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7079,13 +7070,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747228</t>
+          <t>https://artportalen.se/Sighting/120747198</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120747402</v>
+        <v>120747228</v>
       </c>
       <c r="B60" t="n">
         <v>79327</v>
@@ -7123,10 +7114,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480831</v>
+        <v>480890</v>
       </c>
       <c r="R60" t="n">
-        <v>6787737</v>
+        <v>6787571</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7190,54 +7181,57 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747402</t>
+          <t>https://artportalen.se/Sighting/120747228</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112996022</v>
+        <v>120747402</v>
       </c>
       <c r="B61" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480891</v>
+        <v>480831</v>
       </c>
       <c r="R61" t="n">
-        <v>6787557</v>
+        <v>6787737</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7261,12 +7255,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7275,77 +7274,72 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996022</t>
+          <t>https://artportalen.se/Sighting/120747402</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112924074</v>
+        <v>136858154</v>
       </c>
       <c r="B62" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481017</v>
+        <v>480843</v>
       </c>
       <c r="R62" t="n">
-        <v>6787651</v>
+        <v>6787914</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7369,22 +7363,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7399,27 +7383,27 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Andreas Öster, Uno Skog</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924074</t>
+          <t>https://artportalen.se/Sighting/136858154</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112980896</v>
+        <v>112996022</v>
       </c>
       <c r="B63" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7427,43 +7411,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480919</v>
+        <v>480891</v>
       </c>
       <c r="R63" t="n">
-        <v>6787525</v>
+        <v>6787557</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7490,19 +7468,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>09:39</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>09:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7517,24 +7485,24 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112980896</t>
+          <t>https://artportalen.se/Sighting/112996022</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125106308</v>
+        <v>112924074</v>
       </c>
       <c r="B64" t="n">
         <v>57953</v>
@@ -7563,19 +7531,25 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480781</v>
+        <v>481017</v>
       </c>
       <c r="R64" t="n">
-        <v>6787572</v>
+        <v>6787651</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7599,27 +7573,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Hackmärken färska i gran</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7634,27 +7603,27 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125106308</t>
+          <t>https://artportalen.se/Sighting/112924074</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112923064</v>
+        <v>112980896</v>
       </c>
       <c r="B65" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7662,32 +7631,28 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7696,13 +7661,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480817</v>
+        <v>480919</v>
       </c>
       <c r="R65" t="n">
-        <v>6787576</v>
+        <v>6787525</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7726,22 +7691,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7767,16 +7732,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923064</t>
+          <t>https://artportalen.se/Sighting/112980896</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112982228</v>
+        <v>125106308</v>
       </c>
       <c r="B66" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7784,41 +7749,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480787</v>
+        <v>480781</v>
       </c>
       <c r="R66" t="n">
-        <v>6787755</v>
+        <v>6787572</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7842,22 +7803,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Hackmärken färska i gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7872,56 +7838,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112982228</t>
+          <t>https://artportalen.se/Sighting/125106308</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112923140</v>
+        <v>112923064</v>
       </c>
       <c r="B67" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7936,7 +7906,7 @@
         <v>6787576</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7965,7 +7935,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7975,7 +7945,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8001,60 +7971,58 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923140</t>
+          <t>https://artportalen.se/Sighting/112923064</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112923512</v>
+        <v>112982228</v>
       </c>
       <c r="B68" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480733</v>
+        <v>480787</v>
       </c>
       <c r="R68" t="n">
-        <v>6787668</v>
+        <v>6787755</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8078,22 +8046,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8113,19 +8081,19 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923512</t>
+          <t>https://artportalen.se/Sighting/112982228</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112924028</v>
+        <v>112923140</v>
       </c>
       <c r="B69" t="n">
         <v>8455</v>
@@ -8155,19 +8123,24 @@
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481017</v>
+        <v>480817</v>
       </c>
       <c r="R69" t="n">
-        <v>6787651</v>
+        <v>6787576</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8196,7 +8169,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8206,7 +8179,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8232,13 +8205,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924028</t>
+          <t>https://artportalen.se/Sighting/112923140</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112924151</v>
+        <v>112923512</v>
       </c>
       <c r="B70" t="n">
         <v>8455</v>
@@ -8268,19 +8241,24 @@
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480927</v>
+        <v>480733</v>
       </c>
       <c r="R70" t="n">
-        <v>6787699</v>
+        <v>6787668</v>
       </c>
       <c r="S70" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8309,7 +8287,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8319,7 +8297,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8345,13 +8323,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924151</t>
+          <t>https://artportalen.se/Sighting/112923512</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120747281</v>
+        <v>112924028</v>
       </c>
       <c r="B71" t="n">
         <v>8455</v>
@@ -8380,24 +8358,20 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480845</v>
+        <v>481017</v>
       </c>
       <c r="R71" t="n">
-        <v>6787659</v>
+        <v>6787651</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8421,17 +8395,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8440,31 +8419,30 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747281</t>
+          <t>https://artportalen.se/Sighting/112924028</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120747340</v>
+        <v>112924151</v>
       </c>
       <c r="B72" t="n">
         <v>8455</v>
@@ -8493,24 +8471,20 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480847</v>
+        <v>480927</v>
       </c>
       <c r="R72" t="n">
-        <v>6787707</v>
+        <v>6787699</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8534,17 +8508,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8553,34 +8532,33 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747340</t>
+          <t>https://artportalen.se/Sighting/112924151</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135708300</v>
+        <v>120747281</v>
       </c>
       <c r="B73" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8606,24 +8584,24 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480839</v>
+        <v>480845</v>
       </c>
       <c r="R73" t="n">
-        <v>6787636</v>
+        <v>6787659</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8647,22 +8625,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>08:59</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>08:59</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8671,18 +8644,9 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8698,63 +8662,56 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708300</t>
+          <t>https://artportalen.se/Sighting/120747281</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119568643</v>
+        <v>120747340</v>
       </c>
       <c r="B74" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>481007</v>
+        <v>480847</v>
       </c>
       <c r="R74" t="n">
-        <v>6787620</v>
+        <v>6787707</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8781,12 +8738,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8802,27 +8764,27 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568643</t>
+          <t>https://artportalen.se/Sighting/120747340</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125187193</v>
+        <v>135708300</v>
       </c>
       <c r="B75" t="n">
-        <v>104628</v>
+        <v>8463</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8830,43 +8792,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222412</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480717</v>
+        <v>480839</v>
       </c>
       <c r="R75" t="n">
-        <v>6787597</v>
+        <v>6787636</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8893,12 +8851,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8909,66 +8877,88 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125187193</t>
+          <t>https://artportalen.se/Sighting/135708300</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>112996021</v>
+        <v>119568643</v>
       </c>
       <c r="B76" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480899</v>
+        <v>481007</v>
       </c>
       <c r="R76" t="n">
-        <v>6787538</v>
+        <v>6787620</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8995,12 +8985,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9009,71 +8999,81 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996021</t>
+          <t>https://artportalen.se/Sighting/119568643</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121972913</v>
+        <v>125187193</v>
       </c>
       <c r="B77" t="n">
-        <v>79085</v>
+        <v>104628</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>222412</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480935</v>
+        <v>480717</v>
       </c>
       <c r="R77" t="n">
-        <v>6787807</v>
+        <v>6787597</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9097,12 +9097,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9117,27 +9117,27 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972913</t>
+          <t>https://artportalen.se/Sighting/125187193</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119568677</v>
+        <v>112996021</v>
       </c>
       <c r="B78" t="n">
-        <v>91402</v>
+        <v>79085</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9145,41 +9145,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>256703</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480971</v>
+        <v>480899</v>
       </c>
       <c r="R78" t="n">
-        <v>6787547</v>
+        <v>6787538</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9206,12 +9199,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9220,34 +9213,33 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568677</t>
+          <t>https://artportalen.se/Sighting/112996021</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120747144</v>
+        <v>121972913</v>
       </c>
       <c r="B79" t="n">
-        <v>79350</v>
+        <v>79085</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9255,37 +9247,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480904</v>
+        <v>480935</v>
       </c>
       <c r="R79" t="n">
-        <v>6787507</v>
+        <v>6787807</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9312,17 +9301,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9331,34 +9315,33 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747144</t>
+          <t>https://artportalen.se/Sighting/121972913</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120747368</v>
+        <v>119568677</v>
       </c>
       <c r="B80" t="n">
-        <v>79350</v>
+        <v>91402</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9366,37 +9349,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>260591</v>
+        <v>256703</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480840</v>
+        <v>480971</v>
       </c>
       <c r="R80" t="n">
-        <v>6787710</v>
+        <v>6787547</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9423,17 +9410,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>på tall</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9449,24 +9431,24 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747368</t>
+          <t>https://artportalen.se/Sighting/119568677</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125105944</v>
+        <v>120747144</v>
       </c>
       <c r="B81" t="n">
         <v>79350</v>
@@ -9495,19 +9477,22 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481003</v>
+        <v>480904</v>
       </c>
       <c r="R81" t="n">
-        <v>6787803</v>
+        <v>6787507</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9531,22 +9516,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9555,6 +9535,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9572,16 +9553,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125105944</t>
+          <t>https://artportalen.se/Sighting/120747144</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135710473</v>
+        <v>120747368</v>
       </c>
       <c r="B82" t="n">
-        <v>79477</v>
+        <v>79350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9607,16 +9588,19 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Ekentjärn, Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480848</v>
+        <v>480840</v>
       </c>
       <c r="R82" t="n">
-        <v>6787635</v>
+        <v>6787710</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9643,27 +9627,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9672,6 +9646,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9689,16 +9664,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710473</t>
+          <t>https://artportalen.se/Sighting/120747368</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112989992</v>
+        <v>125105944</v>
       </c>
       <c r="B83" t="n">
-        <v>79359</v>
+        <v>79350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9706,37 +9681,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>260591</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481125</v>
+        <v>481003</v>
       </c>
       <c r="R83" t="n">
-        <v>6787708</v>
+        <v>6787803</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9763,17 +9735,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9782,7 +9759,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9794,22 +9770,22 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112989992</t>
+          <t>https://artportalen.se/Sighting/125105944</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121972885</v>
+        <v>135710473</v>
       </c>
       <c r="B84" t="n">
-        <v>91909</v>
+        <v>79477</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9817,34 +9793,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>260591</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481124</v>
+        <v>480848</v>
       </c>
       <c r="R84" t="n">
-        <v>6787703</v>
+        <v>6787635</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9871,12 +9847,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9891,65 +9882,68 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972885</t>
+          <t>https://artportalen.se/Sighting/135710473</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121972895</v>
+        <v>112989992</v>
       </c>
       <c r="B85" t="n">
-        <v>93213</v>
+        <v>79359</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2059</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481073</v>
+        <v>481125</v>
       </c>
       <c r="R85" t="n">
-        <v>6787790</v>
+        <v>6787708</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9973,12 +9967,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9987,55 +9986,56 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972895</t>
+          <t>https://artportalen.se/Sighting/112989992</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112996034</v>
+        <v>121972885</v>
       </c>
       <c r="B86" t="n">
-        <v>92281</v>
+        <v>91909</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10045,10 +10045,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481123</v>
+        <v>481124</v>
       </c>
       <c r="R86" t="n">
-        <v>6787706</v>
+        <v>6787703</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10095,76 +10095,65 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996034</t>
+          <t>https://artportalen.se/Sighting/121972885</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112996037</v>
+        <v>121972895</v>
       </c>
       <c r="B87" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481143</v>
+        <v>481073</v>
       </c>
       <c r="R87" t="n">
-        <v>6787609</v>
+        <v>6787790</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10188,12 +10177,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10202,83 +10191,71 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996037</t>
+          <t>https://artportalen.se/Sighting/121972895</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112996031</v>
+        <v>112996034</v>
       </c>
       <c r="B88" t="n">
-        <v>93209</v>
+        <v>92281</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4366</v>
+        <v>2062</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481063</v>
+        <v>481123</v>
       </c>
       <c r="R88" t="n">
-        <v>6787744</v>
+        <v>6787706</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10333,16 +10310,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996031</t>
+          <t>https://artportalen.se/Sighting/112996034</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>112990060</v>
+        <v>112996037</v>
       </c>
       <c r="B89" t="n">
-        <v>91930</v>
+        <v>93197</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10350,37 +10327,45 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481141</v>
+        <v>481143</v>
       </c>
       <c r="R89" t="n">
-        <v>6787582</v>
+        <v>6787609</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10415,11 +10400,6 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10433,62 +10413,73 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112990060</t>
+          <t>https://artportalen.se/Sighting/112996037</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>112996032</v>
+        <v>112996031</v>
       </c>
       <c r="B90" t="n">
-        <v>91282</v>
+        <v>93209</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5685</v>
+        <v>4366</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481080</v>
+        <v>481063</v>
       </c>
       <c r="R90" t="n">
-        <v>6787730</v>
+        <v>6787744</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10546,51 +10537,54 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996032</t>
+          <t>https://artportalen.se/Sighting/112996031</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112996036</v>
+        <v>112990060</v>
       </c>
       <c r="B91" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481143</v>
+        <v>481141</v>
       </c>
       <c r="R91" t="n">
-        <v>6787598</v>
+        <v>6787582</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10625,85 +10619,83 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996036</t>
+          <t>https://artportalen.se/Sighting/112990060</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112983277</v>
+        <v>112996032</v>
       </c>
       <c r="B92" t="n">
-        <v>57953</v>
+        <v>91282</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>5685</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>481142</v>
+        <v>481080</v>
       </c>
       <c r="R92" t="n">
-        <v>6787700</v>
+        <v>6787730</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10730,19 +10722,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>11:20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10757,70 +10739,65 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983277</t>
+          <t>https://artportalen.se/Sighting/112996032</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>112983978</v>
+        <v>112996036</v>
       </c>
       <c r="B93" t="n">
-        <v>5179</v>
+        <v>79327</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>481104</v>
+        <v>481143</v>
       </c>
       <c r="R93" t="n">
-        <v>6787672</v>
+        <v>6787598</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10847,99 +10824,87 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983978</t>
+          <t>https://artportalen.se/Sighting/112996036</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>112996035</v>
+        <v>112983277</v>
       </c>
       <c r="B94" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>481128</v>
+        <v>481142</v>
       </c>
       <c r="R94" t="n">
-        <v>6787712</v>
+        <v>6787700</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10969,42 +10934,51 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996035</t>
+          <t>https://artportalen.se/Sighting/112983277</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121972923</v>
+        <v>112983978</v>
       </c>
       <c r="B95" t="n">
         <v>5179</v>
@@ -11033,16 +11007,21 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481148</v>
+        <v>481104</v>
       </c>
       <c r="R95" t="n">
-        <v>6787700</v>
+        <v>6787672</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11069,12 +11048,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11083,33 +11072,34 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972923</t>
+          <t>https://artportalen.se/Sighting/112983978</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121972882</v>
+        <v>112996035</v>
       </c>
       <c r="B96" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11117,37 +11107,46 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>481148</v>
+        <v>481128</v>
       </c>
       <c r="R96" t="n">
-        <v>6787700</v>
+        <v>6787712</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11171,12 +11170,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11185,33 +11184,34 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972882</t>
+          <t>https://artportalen.se/Sighting/112996035</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112983991</v>
+        <v>121972923</v>
       </c>
       <c r="B97" t="n">
-        <v>8455</v>
+        <v>5179</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11219,42 +11219,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>481104</v>
+        <v>481148</v>
       </c>
       <c r="R97" t="n">
-        <v>6787672</v>
+        <v>6787700</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11278,22 +11273,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11302,56 +11287,55 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983991</t>
+          <t>https://artportalen.se/Sighting/121972923</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>112996033</v>
+        <v>121972882</v>
       </c>
       <c r="B98" t="n">
-        <v>79085</v>
+        <v>5199</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>105930</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11361,10 +11345,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>481079</v>
+        <v>481148</v>
       </c>
       <c r="R98" t="n">
-        <v>6787734</v>
+        <v>6787700</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11391,12 +11375,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11411,16 +11395,236 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972882</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>112983991</v>
+      </c>
+      <c r="B99" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>481104</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6787672</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983991</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>112996033</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>481079</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6787734</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112996033</t>
         </is>
@@ -11525,6 +11729,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -7388,7 +7388,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Andreas Öster, Uno Skog</t>
+          <t>Uno Skog, Andreas Öster</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -7388,7 +7388,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Uno Skog, Andreas Öster</t>
+          <t>Andreas Öster, Uno Skog</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ100"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112996024</v>
+        <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>92208</v>
+        <v>79508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,21 +1486,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480875</v>
+        <v>481017</v>
       </c>
       <c r="R9" t="n">
-        <v>6787485</v>
+        <v>6787776</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,12 +1540,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,27 +1570,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996024</t>
+          <t>https://artportalen.se/Sighting/136854283</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119565457</v>
+        <v>112996024</v>
       </c>
       <c r="B10" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,39 +1598,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480985</v>
+        <v>480875</v>
       </c>
       <c r="R10" t="n">
-        <v>6787569</v>
+        <v>6787485</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,22 +1652,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:07</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:07</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,34 +1666,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565457</t>
+          <t>https://artportalen.se/Sighting/112996024</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95895917</v>
+        <v>119565457</v>
       </c>
       <c r="B11" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,44 +1700,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480826</v>
+        <v>480985</v>
       </c>
       <c r="R11" t="n">
-        <v>6787548</v>
+        <v>6787569</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,12 +1756,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,24 +1787,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95895917</t>
+          <t>https://artportalen.se/Sighting/119565457</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112996023</v>
+        <v>95895917</v>
       </c>
       <c r="B12" t="n">
         <v>92369</v>
@@ -1830,17 +1832,24 @@
           <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480874</v>
+        <v>480826</v>
       </c>
       <c r="R12" t="n">
-        <v>6787486</v>
+        <v>6787548</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,12 +1876,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,71 +1890,72 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996023</t>
+          <t>https://artportalen.se/Sighting/95895917</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119342591</v>
+        <v>112996023</v>
       </c>
       <c r="B13" t="n">
-        <v>93206</v>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1439</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sammetstaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum martioflavum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Snell, K.A.Harrison &amp; H.A.C.Jacks.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Unnån, Ekentjärnarna, Unnån, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480814</v>
+        <v>480874</v>
       </c>
       <c r="R13" t="n">
-        <v>6787531</v>
+        <v>6787486</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1969,22 +1979,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,65 +1999,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119342591</t>
+          <t>https://artportalen.se/Sighting/112996023</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136854171</v>
+        <v>119342591</v>
       </c>
       <c r="B14" t="n">
-        <v>91117</v>
+        <v>93206</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>1439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Sammetstaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum martioflavum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Snell, K.A.Harrison &amp; H.A.C.Jacks.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480987</v>
+        <v>480814</v>
       </c>
       <c r="R14" t="n">
-        <v>6787699</v>
+        <v>6787531</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2081,12 +2081,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,68 +2111,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136854171</t>
+          <t>https://artportalen.se/Sighting/119342591</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119096505</v>
+        <v>136854171</v>
       </c>
       <c r="B15" t="n">
-        <v>91394</v>
+        <v>91117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2051</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Unnån, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480846</v>
+        <v>480987</v>
       </c>
       <c r="R15" t="n">
-        <v>6787516</v>
+        <v>6787699</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2186,22 +2193,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,39 +2207,33 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>I brant slänt på isälvssediment, mest gran i närheten, tall längre bort.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119096505</t>
+          <t>https://artportalen.se/Sighting/136854171</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112922790</v>
+        <v>119096505</v>
       </c>
       <c r="B16" t="n">
-        <v>93213</v>
+        <v>91394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,47 +2241,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480742</v>
+        <v>480846</v>
       </c>
       <c r="R16" t="n">
-        <v>6787676</v>
+        <v>6787516</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,22 +2298,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,30 +2322,36 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>I brant slänt på isälvssediment, mest gran i närheten, tall längre bort.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922790</t>
+          <t>https://artportalen.se/Sighting/119096505</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121972897</v>
+        <v>112922790</v>
       </c>
       <c r="B17" t="n">
         <v>93213</v>
@@ -2389,20 +2379,30 @@
           <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481022</v>
+        <v>480742</v>
       </c>
       <c r="R17" t="n">
-        <v>6787739</v>
+        <v>6787676</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2426,12 +2426,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2446,24 +2456,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972897</t>
+          <t>https://artportalen.se/Sighting/112922790</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121972898</v>
+        <v>121972897</v>
       </c>
       <c r="B18" t="n">
         <v>93213</v>
@@ -2498,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480829</v>
+        <v>481022</v>
       </c>
       <c r="R18" t="n">
-        <v>6787731</v>
+        <v>6787739</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2559,13 +2569,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972898</t>
+          <t>https://artportalen.se/Sighting/121972897</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121972901</v>
+        <v>121972898</v>
       </c>
       <c r="B19" t="n">
         <v>93213</v>
@@ -2600,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480745</v>
+        <v>480829</v>
       </c>
       <c r="R19" t="n">
-        <v>6787692</v>
+        <v>6787731</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2661,16 +2671,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972901</t>
+          <t>https://artportalen.se/Sighting/121972898</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136457415</v>
+        <v>121972901</v>
       </c>
       <c r="B20" t="n">
-        <v>93427</v>
+        <v>93213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,14 +2708,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, SV Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480744</v>
+        <v>480745</v>
       </c>
       <c r="R20" t="n">
-        <v>6787688</v>
+        <v>6787692</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,22 +2742,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,62 +2762,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136457415</t>
+          <t>https://artportalen.se/Sighting/121972901</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121972912</v>
+        <v>136457415</v>
       </c>
       <c r="B21" t="n">
-        <v>91962</v>
+        <v>93427</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>SV Ekentjärn, SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480966</v>
+        <v>480744</v>
       </c>
       <c r="R21" t="n">
-        <v>6787791</v>
+        <v>6787688</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2844,12 +2844,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2864,27 +2874,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972912</t>
+          <t>https://artportalen.se/Sighting/136457415</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121972884</v>
+        <v>121972912</v>
       </c>
       <c r="B22" t="n">
-        <v>87325</v>
+        <v>91962</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2892,37 +2902,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3690</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480986</v>
+        <v>480966</v>
       </c>
       <c r="R22" t="n">
-        <v>6787836</v>
+        <v>6787791</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,11 +2964,6 @@
           <t>2024-09-03</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2985,16 +2987,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972884</t>
+          <t>https://artportalen.se/Sighting/121972912</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119096496</v>
+        <v>121972884</v>
       </c>
       <c r="B23" t="n">
-        <v>93189</v>
+        <v>87325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3002,21 +3004,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3025,17 +3027,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Unnån, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480846</v>
+        <v>480986</v>
       </c>
       <c r="R23" t="n">
-        <v>6787516</v>
+        <v>6787836</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3059,12 +3061,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Fruktkroppen artbestämd av Carl Jansson i fält.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3073,7 +3080,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3091,13 +3097,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119096496</t>
+          <t>https://artportalen.se/Sighting/121972884</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119565699</v>
+        <v>119096496</v>
       </c>
       <c r="B24" t="n">
         <v>93189</v>
@@ -3125,31 +3131,23 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480853</v>
+        <v>480846</v>
       </c>
       <c r="R24" t="n">
         <v>6787516</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,22 +3171,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3204,24 +3192,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565699</t>
+          <t>https://artportalen.se/Sighting/119096496</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119565742</v>
+        <v>119565699</v>
       </c>
       <c r="B25" t="n">
         <v>93189</v>
@@ -3251,7 +3239,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3263,14 +3251,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Siljansleden, Siljansleden, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480845</v>
+        <v>480853</v>
       </c>
       <c r="R25" t="n">
-        <v>6787511</v>
+        <v>6787516</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3302,7 +3290,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3312,7 +3300,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,13 +3327,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119565742</t>
+          <t>https://artportalen.se/Sighting/119565699</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119566308</v>
+        <v>119565742</v>
       </c>
       <c r="B26" t="n">
         <v>93189</v>
@@ -3375,7 +3363,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3387,14 +3375,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Siljansleden, Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480816</v>
+        <v>480845</v>
       </c>
       <c r="R26" t="n">
-        <v>6787542</v>
+        <v>6787511</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3426,7 +3414,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3436,7 +3424,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3463,13 +3451,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119566308</t>
+          <t>https://artportalen.se/Sighting/119565742</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119568829</v>
+        <v>119566308</v>
       </c>
       <c r="B27" t="n">
         <v>93189</v>
@@ -3499,25 +3487,29 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480735</v>
+        <v>480816</v>
       </c>
       <c r="R27" t="n">
-        <v>6787658</v>
+        <v>6787542</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3544,9 +3536,19 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3562,24 +3564,24 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Lars Johan Klockars, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568829</t>
+          <t>https://artportalen.se/Sighting/119566308</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121972911</v>
+        <v>119568829</v>
       </c>
       <c r="B28" t="n">
         <v>93189</v>
@@ -3607,20 +3609,27 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480843</v>
+        <v>480735</v>
       </c>
       <c r="R28" t="n">
-        <v>6787540</v>
+        <v>6787658</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3644,12 +3653,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3658,33 +3667,34 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972911</t>
+          <t>https://artportalen.se/Sighting/119568829</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112922923</v>
+        <v>121972911</v>
       </c>
       <c r="B29" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3692,38 +3702,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480772</v>
+        <v>480843</v>
       </c>
       <c r="R29" t="n">
-        <v>6787679</v>
+        <v>6787540</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3747,22 +3756,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,24 +3776,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922923</t>
+          <t>https://artportalen.se/Sighting/121972911</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112922930</v>
+        <v>112922923</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3822,16 +3821,7 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3839,13 +3829,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480779</v>
+        <v>480772</v>
       </c>
       <c r="R30" t="n">
-        <v>6787677</v>
+        <v>6787679</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3874,7 +3864,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3884,7 +3874,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3910,13 +3900,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112922930</t>
+          <t>https://artportalen.se/Sighting/112922923</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112923242</v>
+        <v>112922930</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3946,7 +3936,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3961,13 +3951,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480760</v>
+        <v>480779</v>
       </c>
       <c r="R31" t="n">
-        <v>6787645</v>
+        <v>6787677</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3996,7 +3986,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4006,7 +3996,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4032,13 +4022,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923242</t>
+          <t>https://artportalen.se/Sighting/112922930</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112996027</v>
+        <v>112923242</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -4068,7 +4058,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4077,17 +4067,16 @@
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480947</v>
+        <v>480760</v>
       </c>
       <c r="R32" t="n">
-        <v>6787809</v>
+        <v>6787645</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4114,12 +4103,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4128,31 +4127,30 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996027</t>
+          <t>https://artportalen.se/Sighting/112923242</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112996030</v>
+        <v>112996027</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -4182,7 +4180,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4198,10 +4196,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481005</v>
+        <v>480947</v>
       </c>
       <c r="R33" t="n">
-        <v>6787834</v>
+        <v>6787809</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4260,13 +4258,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996030</t>
+          <t>https://artportalen.se/Sighting/112996027</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119545661</v>
+        <v>112996030</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4294,8 +4292,16 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4304,13 +4310,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481008</v>
+        <v>481005</v>
       </c>
       <c r="R34" t="n">
-        <v>6787840</v>
+        <v>6787834</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4334,17 +4340,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>rikligt, tiotals</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4360,24 +4361,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119545661</t>
+          <t>https://artportalen.se/Sighting/112996030</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120837852</v>
+        <v>119545661</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4405,16 +4406,8 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -4423,13 +4416,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481001</v>
+        <v>481008</v>
       </c>
       <c r="R35" t="n">
-        <v>6787844</v>
+        <v>6787840</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4453,12 +4446,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>rikligt, tiotals</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4474,24 +4472,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120837852</t>
+          <t>https://artportalen.se/Sighting/119545661</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121972915</v>
+        <v>120837852</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4519,14 +4517,25 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480914</v>
+        <v>481001</v>
       </c>
       <c r="R36" t="n">
         <v>6787844</v>
@@ -4556,12 +4565,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,30 +4579,31 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972915</t>
+          <t>https://artportalen.se/Sighting/120837852</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121972916</v>
+        <v>121972915</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4628,10 +4638,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480915</v>
+        <v>480914</v>
       </c>
       <c r="R37" t="n">
-        <v>6787807</v>
+        <v>6787844</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4689,13 +4699,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972916</t>
+          <t>https://artportalen.se/Sighting/121972915</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121972917</v>
+        <v>121972916</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4730,10 +4740,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480797</v>
+        <v>480915</v>
       </c>
       <c r="R38" t="n">
-        <v>6787722</v>
+        <v>6787807</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4791,13 +4801,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972917</t>
+          <t>https://artportalen.se/Sighting/121972916</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121972918</v>
+        <v>121972917</v>
       </c>
       <c r="B39" t="n">
         <v>93197</v>
@@ -4832,10 +4842,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480812</v>
+        <v>480797</v>
       </c>
       <c r="R39" t="n">
-        <v>6787702</v>
+        <v>6787722</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4893,13 +4903,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972918</t>
+          <t>https://artportalen.se/Sighting/121972917</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121972919</v>
+        <v>121972918</v>
       </c>
       <c r="B40" t="n">
         <v>93197</v>
@@ -4934,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480773</v>
+        <v>480812</v>
       </c>
       <c r="R40" t="n">
-        <v>6787678</v>
+        <v>6787702</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4995,13 +5005,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972919</t>
+          <t>https://artportalen.se/Sighting/121972918</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121972920</v>
+        <v>121972919</v>
       </c>
       <c r="B41" t="n">
         <v>93197</v>
@@ -5036,10 +5046,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480994</v>
+        <v>480773</v>
       </c>
       <c r="R41" t="n">
-        <v>6787675</v>
+        <v>6787678</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5097,13 +5107,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972920</t>
+          <t>https://artportalen.se/Sighting/121972919</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121972921</v>
+        <v>121972920</v>
       </c>
       <c r="B42" t="n">
         <v>93197</v>
@@ -5138,10 +5148,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480761</v>
+        <v>480994</v>
       </c>
       <c r="R42" t="n">
-        <v>6787650</v>
+        <v>6787675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5199,13 +5209,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972921</t>
+          <t>https://artportalen.se/Sighting/121972920</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121972922</v>
+        <v>121972921</v>
       </c>
       <c r="B43" t="n">
         <v>93197</v>
@@ -5240,10 +5250,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480796</v>
+        <v>480761</v>
       </c>
       <c r="R43" t="n">
-        <v>6787645</v>
+        <v>6787650</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5301,13 +5311,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972922</t>
+          <t>https://artportalen.se/Sighting/121972921</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127640071</v>
+        <v>121972922</v>
       </c>
       <c r="B44" t="n">
         <v>93197</v>
@@ -5338,14 +5348,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480961</v>
+        <v>480796</v>
       </c>
       <c r="R44" t="n">
-        <v>6787858</v>
+        <v>6787645</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5372,12 +5382,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5392,27 +5402,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alexander Singer, Andreas Öster, Cecilia Öster, Lina Lejonberg, Malte Lindberg</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127640071</t>
+          <t>https://artportalen.se/Sighting/121972922</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136489706</v>
+        <v>127640071</v>
       </c>
       <c r="B45" t="n">
-        <v>93411</v>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5440,17 +5450,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481015</v>
+        <v>480961</v>
       </c>
       <c r="R45" t="n">
-        <v>6787850</v>
+        <v>6787858</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5474,22 +5484,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5504,24 +5504,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+          <t>Alexander Singer, Andreas Öster, Cecilia Öster, Lina Lejonberg, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136489706</t>
+          <t>https://artportalen.se/Sighting/127640071</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136489707</v>
+        <v>136489706</v>
       </c>
       <c r="B46" t="n">
         <v>93411</v>
@@ -5556,13 +5556,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481006</v>
+        <v>481015</v>
       </c>
       <c r="R46" t="n">
-        <v>6787842</v>
+        <v>6787850</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5627,16 +5627,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136489707</t>
+          <t>https://artportalen.se/Sighting/136489706</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121972907</v>
+        <v>136489707</v>
       </c>
       <c r="B47" t="n">
-        <v>93209</v>
+        <v>93411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5644,21 +5644,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5668,13 +5668,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480936</v>
+        <v>481006</v>
       </c>
       <c r="R47" t="n">
-        <v>6787692</v>
+        <v>6787842</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5698,12 +5698,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5718,49 +5728,49 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972907</t>
+          <t>https://artportalen.se/Sighting/136489707</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112996025</v>
+        <v>121972907</v>
       </c>
       <c r="B48" t="n">
-        <v>91893</v>
+        <v>93209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4660</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5770,10 +5780,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480874</v>
+        <v>480936</v>
       </c>
       <c r="R48" t="n">
-        <v>6787479</v>
+        <v>6787692</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5800,12 +5810,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5820,72 +5830,65 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996025</t>
+          <t>https://artportalen.se/Sighting/121972907</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112996029</v>
+        <v>112996025</v>
       </c>
       <c r="B49" t="n">
-        <v>90522</v>
+        <v>91893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4962</v>
+        <v>4660</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481007</v>
+        <v>480874</v>
       </c>
       <c r="R49" t="n">
-        <v>6787835</v>
+        <v>6787479</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5940,16 +5943,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996029</t>
+          <t>https://artportalen.se/Sighting/112996025</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112914094</v>
+        <v>112996029</v>
       </c>
       <c r="B50" t="n">
-        <v>91930</v>
+        <v>90522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5957,37 +5960,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>4962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480743</v>
+        <v>481007</v>
       </c>
       <c r="R50" t="n">
-        <v>6787694</v>
+        <v>6787835</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6014,12 +6021,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6028,34 +6035,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914094</t>
+          <t>https://artportalen.se/Sighting/112996029</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112923898</v>
+        <v>112914094</v>
       </c>
       <c r="B51" t="n">
-        <v>93223</v>
+        <v>91930</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6063,45 +6069,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480942</v>
+        <v>480743</v>
       </c>
       <c r="R51" t="n">
-        <v>6787720</v>
+        <v>6787694</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6128,22 +6126,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6159,27 +6147,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923898</t>
+          <t>https://artportalen.se/Sighting/112914094</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112996028</v>
+        <v>112923898</v>
       </c>
       <c r="B52" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6187,37 +6175,48 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480995</v>
+        <v>480942</v>
       </c>
       <c r="R52" t="n">
-        <v>6787829</v>
+        <v>6787720</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6241,12 +6240,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6255,71 +6264,69 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996028</t>
+          <t>https://artportalen.se/Sighting/112923898</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>96117407</v>
+        <v>112996028</v>
       </c>
       <c r="B53" t="n">
-        <v>79327</v>
+        <v>93235</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480781</v>
+        <v>480995</v>
       </c>
       <c r="R53" t="n">
-        <v>6787572</v>
+        <v>6787829</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6346,12 +6353,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6360,46 +6367,30 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96117407</t>
+          <t>https://artportalen.se/Sighting/112996028</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112914136</v>
+        <v>96117407</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6433,14 +6424,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480780</v>
+        <v>480781</v>
       </c>
       <c r="R54" t="n">
-        <v>6787640</v>
+        <v>6787572</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6467,17 +6458,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6490,6 +6476,21 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
@@ -6504,13 +6505,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914136</t>
+          <t>https://artportalen.se/Sighting/96117407</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112923198</v>
+        <v>112914136</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6539,20 +6540,22 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480817</v>
+        <v>480780</v>
       </c>
       <c r="R55" t="n">
-        <v>6787576</v>
+        <v>6787640</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6576,27 +6579,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6605,30 +6598,31 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923198</t>
+          <t>https://artportalen.se/Sighting/112914136</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112923608</v>
+        <v>112923198</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6664,13 +6658,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480882</v>
+        <v>480817</v>
       </c>
       <c r="R56" t="n">
-        <v>6787809</v>
+        <v>6787576</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6699,7 +6693,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6709,7 +6703,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6735,13 +6734,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923608</t>
+          <t>https://artportalen.se/Sighting/112923198</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112924155</v>
+        <v>112923608</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6777,13 +6776,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480927</v>
+        <v>480882</v>
       </c>
       <c r="R57" t="n">
-        <v>6787699</v>
+        <v>6787809</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6812,7 +6811,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6822,7 +6821,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6848,13 +6847,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924155</t>
+          <t>https://artportalen.se/Sighting/112923608</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120747170</v>
+        <v>112924155</v>
       </c>
       <c r="B58" t="n">
         <v>79327</v>
@@ -6883,22 +6882,20 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480886</v>
+        <v>480927</v>
       </c>
       <c r="R58" t="n">
-        <v>6787539</v>
+        <v>6787699</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6922,17 +6919,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6941,31 +6943,30 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747170</t>
+          <t>https://artportalen.se/Sighting/112924155</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120747198</v>
+        <v>120747170</v>
       </c>
       <c r="B59" t="n">
         <v>79327</v>
@@ -7003,10 +7004,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480878</v>
+        <v>480886</v>
       </c>
       <c r="R59" t="n">
-        <v>6787512</v>
+        <v>6787539</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7070,13 +7071,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747198</t>
+          <t>https://artportalen.se/Sighting/120747170</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120747228</v>
+        <v>120747198</v>
       </c>
       <c r="B60" t="n">
         <v>79327</v>
@@ -7114,10 +7115,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480890</v>
+        <v>480878</v>
       </c>
       <c r="R60" t="n">
-        <v>6787571</v>
+        <v>6787512</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7181,13 +7182,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747228</t>
+          <t>https://artportalen.se/Sighting/120747198</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120747402</v>
+        <v>120747228</v>
       </c>
       <c r="B61" t="n">
         <v>79327</v>
@@ -7225,10 +7226,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480831</v>
+        <v>480890</v>
       </c>
       <c r="R61" t="n">
-        <v>6787737</v>
+        <v>6787571</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7292,16 +7293,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747402</t>
+          <t>https://artportalen.se/Sighting/120747228</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136858154</v>
+        <v>120747402</v>
       </c>
       <c r="B62" t="n">
-        <v>79476</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7327,16 +7328,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480843</v>
+        <v>480831</v>
       </c>
       <c r="R62" t="n">
-        <v>6787914</v>
+        <v>6787737</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7363,12 +7367,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7377,55 +7386,56 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Andreas Öster, Uno Skog</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136858154</t>
+          <t>https://artportalen.se/Sighting/120747402</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112996022</v>
+        <v>136854286</v>
       </c>
       <c r="B63" t="n">
-        <v>79946</v>
+        <v>79476</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7435,13 +7445,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480891</v>
+        <v>481017</v>
       </c>
       <c r="R63" t="n">
-        <v>6787557</v>
+        <v>6787776</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7465,12 +7475,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7485,71 +7505,65 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996022</t>
+          <t>https://artportalen.se/Sighting/136854286</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112924074</v>
+        <v>136858154</v>
       </c>
       <c r="B64" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481017</v>
+        <v>480843</v>
       </c>
       <c r="R64" t="n">
-        <v>6787651</v>
+        <v>6787914</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7573,22 +7587,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7603,27 +7607,27 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Andreas Öster, Uno Skog</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924074</t>
+          <t>https://artportalen.se/Sighting/136858154</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112980896</v>
+        <v>112996022</v>
       </c>
       <c r="B65" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7631,43 +7635,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480919</v>
+        <v>480891</v>
       </c>
       <c r="R65" t="n">
-        <v>6787525</v>
+        <v>6787557</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7694,19 +7692,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:39</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7721,24 +7709,24 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112980896</t>
+          <t>https://artportalen.se/Sighting/112996022</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125106308</v>
+        <v>112924074</v>
       </c>
       <c r="B66" t="n">
         <v>57953</v>
@@ -7767,19 +7755,25 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480781</v>
+        <v>481017</v>
       </c>
       <c r="R66" t="n">
-        <v>6787572</v>
+        <v>6787651</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7803,27 +7797,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Hackmärken färska i gran</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7838,27 +7827,27 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125106308</t>
+          <t>https://artportalen.se/Sighting/112924074</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112923064</v>
+        <v>112980896</v>
       </c>
       <c r="B67" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7866,32 +7855,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7900,13 +7885,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480817</v>
+        <v>480919</v>
       </c>
       <c r="R67" t="n">
-        <v>6787576</v>
+        <v>6787525</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7930,22 +7915,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7971,16 +7956,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923064</t>
+          <t>https://artportalen.se/Sighting/112980896</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112982228</v>
+        <v>125106308</v>
       </c>
       <c r="B68" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7988,41 +7973,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480787</v>
+        <v>480781</v>
       </c>
       <c r="R68" t="n">
-        <v>6787755</v>
+        <v>6787572</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8046,22 +8027,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Hackmärken färska i gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8076,56 +8062,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112982228</t>
+          <t>https://artportalen.se/Sighting/125106308</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112923140</v>
+        <v>112923064</v>
       </c>
       <c r="B69" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8140,7 +8130,7 @@
         <v>6787576</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8169,7 +8159,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8179,7 +8169,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8205,60 +8195,58 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923140</t>
+          <t>https://artportalen.se/Sighting/112923064</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112923512</v>
+        <v>112982228</v>
       </c>
       <c r="B70" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480733</v>
+        <v>480787</v>
       </c>
       <c r="R70" t="n">
-        <v>6787668</v>
+        <v>6787755</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8282,22 +8270,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8317,19 +8305,19 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923512</t>
+          <t>https://artportalen.se/Sighting/112982228</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112924028</v>
+        <v>112923140</v>
       </c>
       <c r="B71" t="n">
         <v>8455</v>
@@ -8359,19 +8347,24 @@
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481017</v>
+        <v>480817</v>
       </c>
       <c r="R71" t="n">
-        <v>6787651</v>
+        <v>6787576</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8400,7 +8393,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8410,7 +8403,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8436,13 +8429,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924028</t>
+          <t>https://artportalen.se/Sighting/112923140</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112924151</v>
+        <v>112923512</v>
       </c>
       <c r="B72" t="n">
         <v>8455</v>
@@ -8472,19 +8465,24 @@
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480927</v>
+        <v>480733</v>
       </c>
       <c r="R72" t="n">
-        <v>6787699</v>
+        <v>6787668</v>
       </c>
       <c r="S72" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8513,7 +8511,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8523,7 +8521,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8549,13 +8547,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924151</t>
+          <t>https://artportalen.se/Sighting/112923512</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120747281</v>
+        <v>112924028</v>
       </c>
       <c r="B73" t="n">
         <v>8455</v>
@@ -8584,24 +8582,20 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480845</v>
+        <v>481017</v>
       </c>
       <c r="R73" t="n">
-        <v>6787659</v>
+        <v>6787651</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8625,17 +8619,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8644,31 +8643,30 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747281</t>
+          <t>https://artportalen.se/Sighting/112924028</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120747340</v>
+        <v>112924151</v>
       </c>
       <c r="B74" t="n">
         <v>8455</v>
@@ -8697,24 +8695,20 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480847</v>
+        <v>480927</v>
       </c>
       <c r="R74" t="n">
-        <v>6787707</v>
+        <v>6787699</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8738,17 +8732,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8757,34 +8756,33 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747340</t>
+          <t>https://artportalen.se/Sighting/112924151</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135708300</v>
+        <v>120747281</v>
       </c>
       <c r="B75" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8810,24 +8808,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480839</v>
+        <v>480845</v>
       </c>
       <c r="R75" t="n">
-        <v>6787636</v>
+        <v>6787659</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8851,22 +8849,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>08:59</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>08:59</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8875,18 +8868,9 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8902,63 +8886,56 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708300</t>
+          <t>https://artportalen.se/Sighting/120747281</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119568643</v>
+        <v>120747340</v>
       </c>
       <c r="B76" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481007</v>
+        <v>480847</v>
       </c>
       <c r="R76" t="n">
-        <v>6787620</v>
+        <v>6787707</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8985,12 +8962,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9006,27 +8988,27 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568643</t>
+          <t>https://artportalen.se/Sighting/120747340</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125187193</v>
+        <v>135708300</v>
       </c>
       <c r="B77" t="n">
-        <v>104628</v>
+        <v>8463</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9034,43 +9016,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222412</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480717</v>
+        <v>480839</v>
       </c>
       <c r="R77" t="n">
-        <v>6787597</v>
+        <v>6787636</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9097,12 +9075,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9113,66 +9101,88 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125187193</t>
+          <t>https://artportalen.se/Sighting/135708300</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>112996021</v>
+        <v>119568643</v>
       </c>
       <c r="B78" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480899</v>
+        <v>481007</v>
       </c>
       <c r="R78" t="n">
-        <v>6787538</v>
+        <v>6787620</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9199,12 +9209,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9213,71 +9223,81 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996021</t>
+          <t>https://artportalen.se/Sighting/119568643</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121972913</v>
+        <v>125187193</v>
       </c>
       <c r="B79" t="n">
-        <v>79085</v>
+        <v>104628</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>222412</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480935</v>
+        <v>480717</v>
       </c>
       <c r="R79" t="n">
-        <v>6787807</v>
+        <v>6787597</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9301,12 +9321,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9321,27 +9341,27 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972913</t>
+          <t>https://artportalen.se/Sighting/125187193</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119568677</v>
+        <v>112996021</v>
       </c>
       <c r="B80" t="n">
-        <v>91402</v>
+        <v>79085</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9349,41 +9369,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>256703</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480971</v>
+        <v>480899</v>
       </c>
       <c r="R80" t="n">
-        <v>6787547</v>
+        <v>6787538</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9410,12 +9423,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9424,34 +9437,33 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568677</t>
+          <t>https://artportalen.se/Sighting/112996021</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120747144</v>
+        <v>121972913</v>
       </c>
       <c r="B81" t="n">
-        <v>79350</v>
+        <v>79085</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9459,37 +9471,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480904</v>
+        <v>480935</v>
       </c>
       <c r="R81" t="n">
-        <v>6787507</v>
+        <v>6787807</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9516,17 +9525,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9535,34 +9539,33 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747144</t>
+          <t>https://artportalen.se/Sighting/121972913</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120747368</v>
+        <v>119568677</v>
       </c>
       <c r="B82" t="n">
-        <v>79350</v>
+        <v>91402</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9570,37 +9573,41 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>260591</v>
+        <v>256703</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480840</v>
+        <v>480971</v>
       </c>
       <c r="R82" t="n">
-        <v>6787710</v>
+        <v>6787547</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9627,17 +9634,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>på tall</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9653,24 +9655,24 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747368</t>
+          <t>https://artportalen.se/Sighting/119568677</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125105944</v>
+        <v>120747144</v>
       </c>
       <c r="B83" t="n">
         <v>79350</v>
@@ -9699,19 +9701,22 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481003</v>
+        <v>480904</v>
       </c>
       <c r="R83" t="n">
-        <v>6787803</v>
+        <v>6787507</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9735,22 +9740,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9759,6 +9759,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9776,16 +9777,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125105944</t>
+          <t>https://artportalen.se/Sighting/120747144</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135710473</v>
+        <v>120747368</v>
       </c>
       <c r="B84" t="n">
-        <v>79477</v>
+        <v>79350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9811,16 +9812,19 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ekentjärn, Ekentjärn, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480848</v>
+        <v>480840</v>
       </c>
       <c r="R84" t="n">
-        <v>6787635</v>
+        <v>6787710</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9847,27 +9851,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9876,6 +9870,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9893,16 +9888,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710473</t>
+          <t>https://artportalen.se/Sighting/120747368</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112989992</v>
+        <v>125105944</v>
       </c>
       <c r="B85" t="n">
-        <v>79359</v>
+        <v>79350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9910,37 +9905,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>260591</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481125</v>
+        <v>481003</v>
       </c>
       <c r="R85" t="n">
-        <v>6787708</v>
+        <v>6787803</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9967,17 +9959,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9986,7 +9983,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9998,22 +9994,22 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112989992</t>
+          <t>https://artportalen.se/Sighting/125105944</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121972885</v>
+        <v>135710473</v>
       </c>
       <c r="B86" t="n">
-        <v>91909</v>
+        <v>79477</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10021,34 +10017,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>260591</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481124</v>
+        <v>480848</v>
       </c>
       <c r="R86" t="n">
-        <v>6787703</v>
+        <v>6787635</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10075,12 +10071,27 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10095,65 +10106,68 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972885</t>
+          <t>https://artportalen.se/Sighting/135710473</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121972895</v>
+        <v>112989992</v>
       </c>
       <c r="B87" t="n">
-        <v>93213</v>
+        <v>79359</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2059</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481073</v>
+        <v>481125</v>
       </c>
       <c r="R87" t="n">
-        <v>6787790</v>
+        <v>6787708</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10177,12 +10191,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10191,55 +10210,56 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972895</t>
+          <t>https://artportalen.se/Sighting/112989992</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112996034</v>
+        <v>121972885</v>
       </c>
       <c r="B88" t="n">
-        <v>92281</v>
+        <v>91909</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10249,10 +10269,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481123</v>
+        <v>481124</v>
       </c>
       <c r="R88" t="n">
-        <v>6787706</v>
+        <v>6787703</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10279,12 +10299,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10299,76 +10319,65 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996034</t>
+          <t>https://artportalen.se/Sighting/121972885</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>112996037</v>
+        <v>121972895</v>
       </c>
       <c r="B89" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481143</v>
+        <v>481073</v>
       </c>
       <c r="R89" t="n">
-        <v>6787609</v>
+        <v>6787790</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10392,12 +10401,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10406,83 +10415,71 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996037</t>
+          <t>https://artportalen.se/Sighting/121972895</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>112996031</v>
+        <v>112996034</v>
       </c>
       <c r="B90" t="n">
-        <v>93209</v>
+        <v>92281</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4366</v>
+        <v>2062</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481063</v>
+        <v>481123</v>
       </c>
       <c r="R90" t="n">
-        <v>6787744</v>
+        <v>6787706</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10537,16 +10534,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996031</t>
+          <t>https://artportalen.se/Sighting/112996034</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112990060</v>
+        <v>112996037</v>
       </c>
       <c r="B91" t="n">
-        <v>91930</v>
+        <v>93197</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10554,37 +10551,45 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481141</v>
+        <v>481143</v>
       </c>
       <c r="R91" t="n">
-        <v>6787582</v>
+        <v>6787609</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10619,11 +10624,6 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10637,62 +10637,73 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112990060</t>
+          <t>https://artportalen.se/Sighting/112996037</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112996032</v>
+        <v>112996031</v>
       </c>
       <c r="B92" t="n">
-        <v>91282</v>
+        <v>93209</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5685</v>
+        <v>4366</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>481080</v>
+        <v>481063</v>
       </c>
       <c r="R92" t="n">
-        <v>6787730</v>
+        <v>6787744</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10750,51 +10761,54 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996032</t>
+          <t>https://artportalen.se/Sighting/112996031</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>112996036</v>
+        <v>112990060</v>
       </c>
       <c r="B93" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>481143</v>
+        <v>481141</v>
       </c>
       <c r="R93" t="n">
-        <v>6787598</v>
+        <v>6787582</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10829,85 +10843,83 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996036</t>
+          <t>https://artportalen.se/Sighting/112990060</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>112983277</v>
+        <v>112996032</v>
       </c>
       <c r="B94" t="n">
-        <v>57953</v>
+        <v>91282</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>5685</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>481142</v>
+        <v>481080</v>
       </c>
       <c r="R94" t="n">
-        <v>6787700</v>
+        <v>6787730</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10934,19 +10946,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10961,70 +10963,65 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983277</t>
+          <t>https://artportalen.se/Sighting/112996032</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>112983978</v>
+        <v>112996036</v>
       </c>
       <c r="B95" t="n">
-        <v>5179</v>
+        <v>79327</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481104</v>
+        <v>481143</v>
       </c>
       <c r="R95" t="n">
-        <v>6787672</v>
+        <v>6787598</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11051,99 +11048,87 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983978</t>
+          <t>https://artportalen.se/Sighting/112996036</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>112996035</v>
+        <v>112983277</v>
       </c>
       <c r="B96" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>481128</v>
+        <v>481142</v>
       </c>
       <c r="R96" t="n">
-        <v>6787712</v>
+        <v>6787700</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11173,42 +11158,51 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996035</t>
+          <t>https://artportalen.se/Sighting/112983277</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121972923</v>
+        <v>112983978</v>
       </c>
       <c r="B97" t="n">
         <v>5179</v>
@@ -11237,16 +11231,21 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>481148</v>
+        <v>481104</v>
       </c>
       <c r="R97" t="n">
-        <v>6787700</v>
+        <v>6787672</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11273,12 +11272,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11287,33 +11296,34 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972923</t>
+          <t>https://artportalen.se/Sighting/112983978</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121972882</v>
+        <v>112996035</v>
       </c>
       <c r="B98" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11321,37 +11331,46 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>481148</v>
+        <v>481128</v>
       </c>
       <c r="R98" t="n">
-        <v>6787700</v>
+        <v>6787712</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11375,12 +11394,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11389,33 +11408,34 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972882</t>
+          <t>https://artportalen.se/Sighting/112996035</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>112983991</v>
+        <v>121972923</v>
       </c>
       <c r="B99" t="n">
-        <v>8455</v>
+        <v>5179</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11423,42 +11443,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>481104</v>
+        <v>481148</v>
       </c>
       <c r="R99" t="n">
-        <v>6787672</v>
+        <v>6787700</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11482,22 +11497,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11506,56 +11511,55 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983991</t>
+          <t>https://artportalen.se/Sighting/121972923</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>112996033</v>
+        <v>121972882</v>
       </c>
       <c r="B100" t="n">
-        <v>79085</v>
+        <v>5199</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>105930</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11565,10 +11569,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>481079</v>
+        <v>481148</v>
       </c>
       <c r="R100" t="n">
-        <v>6787734</v>
+        <v>6787700</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11595,12 +11599,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11615,16 +11619,236 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972882</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>112983991</v>
+      </c>
+      <c r="B101" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>481104</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6787672</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983991</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>112996033</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>481079</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6787734</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112996033</t>
         </is>
@@ -11731,6 +11955,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136854171</v>
       </c>
       <c r="B15" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136457415</v>
       </c>
       <c r="B21" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136489706</v>
       </c>
       <c r="B46" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bo karlstens, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5636,7 +5636,7 @@
         <v>136489707</v>
       </c>
       <c r="B47" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7413,7 +7413,7 @@
         <v>136854286</v>
       </c>
       <c r="B63" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>136858154</v>
       </c>
       <c r="B64" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136854171</v>
       </c>
       <c r="B15" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136457415</v>
       </c>
       <c r="B21" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136489706</v>
       </c>
       <c r="B46" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bo karlstens, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5636,7 +5636,7 @@
         <v>136489707</v>
       </c>
       <c r="B47" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7413,7 +7413,7 @@
         <v>136854286</v>
       </c>
       <c r="B63" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>136858154</v>
       </c>
       <c r="B64" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ102"/>
+  <dimension ref="A1:AZ116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5847,32 +5847,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112996025</v>
+        <v>137092068</v>
       </c>
       <c r="B49" t="n">
-        <v>91893</v>
+        <v>93427</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4660</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5882,13 +5882,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480874</v>
+        <v>481001</v>
       </c>
       <c r="R49" t="n">
-        <v>6787479</v>
+        <v>6787837</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5912,12 +5912,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5932,72 +5942,65 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996025</t>
+          <t>https://artportalen.se/Sighting/137092068</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112996029</v>
+        <v>112996025</v>
       </c>
       <c r="B50" t="n">
-        <v>90522</v>
+        <v>91893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4962</v>
+        <v>4660</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481007</v>
+        <v>480874</v>
       </c>
       <c r="R50" t="n">
-        <v>6787835</v>
+        <v>6787479</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6052,16 +6055,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996029</t>
+          <t>https://artportalen.se/Sighting/112996025</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112914094</v>
+        <v>112996029</v>
       </c>
       <c r="B51" t="n">
-        <v>91930</v>
+        <v>90522</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6069,37 +6072,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>4962</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480743</v>
+        <v>481007</v>
       </c>
       <c r="R51" t="n">
-        <v>6787694</v>
+        <v>6787835</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6126,12 +6133,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6140,34 +6147,33 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914094</t>
+          <t>https://artportalen.se/Sighting/112996029</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112923898</v>
+        <v>112914094</v>
       </c>
       <c r="B52" t="n">
-        <v>93223</v>
+        <v>91930</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6175,45 +6181,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480942</v>
+        <v>480743</v>
       </c>
       <c r="R52" t="n">
-        <v>6787720</v>
+        <v>6787694</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6240,22 +6238,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6271,27 +6259,27 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923898</t>
+          <t>https://artportalen.se/Sighting/112914094</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112996028</v>
+        <v>112923898</v>
       </c>
       <c r="B53" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6299,37 +6287,48 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480995</v>
+        <v>480942</v>
       </c>
       <c r="R53" t="n">
-        <v>6787829</v>
+        <v>6787720</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6353,12 +6352,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6367,71 +6376,69 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996028</t>
+          <t>https://artportalen.se/Sighting/112923898</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>96117407</v>
+        <v>112996028</v>
       </c>
       <c r="B54" t="n">
-        <v>79327</v>
+        <v>93235</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480781</v>
+        <v>480995</v>
       </c>
       <c r="R54" t="n">
-        <v>6787572</v>
+        <v>6787829</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6458,12 +6465,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6472,46 +6479,30 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96117407</t>
+          <t>https://artportalen.se/Sighting/112996028</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112914136</v>
+        <v>96117407</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6545,14 +6536,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>SV Ekentjärn, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480780</v>
+        <v>480781</v>
       </c>
       <c r="R55" t="n">
-        <v>6787640</v>
+        <v>6787572</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6579,17 +6570,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6602,6 +6588,21 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
@@ -6616,13 +6617,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112914136</t>
+          <t>https://artportalen.se/Sighting/96117407</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112923198</v>
+        <v>112914136</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6651,20 +6652,22 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>SV Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480817</v>
+        <v>480780</v>
       </c>
       <c r="R56" t="n">
-        <v>6787576</v>
+        <v>6787640</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6688,27 +6691,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På många tallar, i stora sjok längs vissa tallstammar, även på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6717,30 +6710,31 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923198</t>
+          <t>https://artportalen.se/Sighting/112914136</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112923608</v>
+        <v>112923198</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6776,13 +6770,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480882</v>
+        <v>480817</v>
       </c>
       <c r="R57" t="n">
-        <v>6787809</v>
+        <v>6787576</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6811,7 +6805,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6821,7 +6815,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6847,13 +6846,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923608</t>
+          <t>https://artportalen.se/Sighting/112923198</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112924155</v>
+        <v>112923608</v>
       </c>
       <c r="B58" t="n">
         <v>79327</v>
@@ -6889,13 +6888,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480927</v>
+        <v>480882</v>
       </c>
       <c r="R58" t="n">
-        <v>6787699</v>
+        <v>6787809</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6924,7 +6923,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6934,7 +6933,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6960,13 +6959,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924155</t>
+          <t>https://artportalen.se/Sighting/112923608</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120747170</v>
+        <v>112924155</v>
       </c>
       <c r="B59" t="n">
         <v>79327</v>
@@ -6995,22 +6994,20 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480886</v>
+        <v>480927</v>
       </c>
       <c r="R59" t="n">
-        <v>6787539</v>
+        <v>6787699</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7034,17 +7031,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7053,31 +7055,30 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747170</t>
+          <t>https://artportalen.se/Sighting/112924155</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120747198</v>
+        <v>120747170</v>
       </c>
       <c r="B60" t="n">
         <v>79327</v>
@@ -7115,10 +7116,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480878</v>
+        <v>480886</v>
       </c>
       <c r="R60" t="n">
-        <v>6787512</v>
+        <v>6787539</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7182,13 +7183,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747198</t>
+          <t>https://artportalen.se/Sighting/120747170</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120747228</v>
+        <v>120747198</v>
       </c>
       <c r="B61" t="n">
         <v>79327</v>
@@ -7226,10 +7227,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480890</v>
+        <v>480878</v>
       </c>
       <c r="R61" t="n">
-        <v>6787571</v>
+        <v>6787512</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7293,13 +7294,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747228</t>
+          <t>https://artportalen.se/Sighting/120747198</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120747402</v>
+        <v>120747228</v>
       </c>
       <c r="B62" t="n">
         <v>79327</v>
@@ -7337,10 +7338,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480831</v>
+        <v>480890</v>
       </c>
       <c r="R62" t="n">
-        <v>6787737</v>
+        <v>6787571</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7404,16 +7405,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747402</t>
+          <t>https://artportalen.se/Sighting/120747228</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136854286</v>
+        <v>120747402</v>
       </c>
       <c r="B63" t="n">
-        <v>79482</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7439,19 +7440,22 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481017</v>
+        <v>480831</v>
       </c>
       <c r="R63" t="n">
-        <v>6787776</v>
+        <v>6787737</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7475,22 +7479,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:54</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:54</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7499,30 +7498,31 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136854286</t>
+          <t>https://artportalen.se/Sighting/120747402</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136858154</v>
+        <v>136854286</v>
       </c>
       <c r="B64" t="n">
         <v>79482</v>
@@ -7553,17 +7553,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480843</v>
+        <v>481017</v>
       </c>
       <c r="R64" t="n">
-        <v>6787914</v>
+        <v>6787776</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7590,9 +7590,19 @@
           <t>2026-09-25</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7607,65 +7617,65 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Andreas Öster, Uno Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136858154</t>
+          <t>https://artportalen.se/Sighting/136854286</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112996022</v>
+        <v>136858154</v>
       </c>
       <c r="B65" t="n">
-        <v>79946</v>
+        <v>79482</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480891</v>
+        <v>480843</v>
       </c>
       <c r="R65" t="n">
-        <v>6787557</v>
+        <v>6787914</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7689,12 +7699,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7709,71 +7719,65 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Andreas Öster, Uno Skog</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996022</t>
+          <t>https://artportalen.se/Sighting/136858154</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112924074</v>
+        <v>137092050</v>
       </c>
       <c r="B66" t="n">
-        <v>57953</v>
+        <v>79482</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481017</v>
+        <v>480938</v>
       </c>
       <c r="R66" t="n">
-        <v>6787651</v>
+        <v>6787869</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7797,22 +7801,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7827,68 +7831,62 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924074</t>
+          <t>https://artportalen.se/Sighting/137092050</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112980896</v>
+        <v>137092051</v>
       </c>
       <c r="B67" t="n">
-        <v>57953</v>
+        <v>79482</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480919</v>
+        <v>480915</v>
       </c>
       <c r="R67" t="n">
-        <v>6787525</v>
+        <v>6787874</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7915,22 +7913,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7945,65 +7943,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112980896</t>
+          <t>https://artportalen.se/Sighting/137092051</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125106308</v>
+        <v>137092052</v>
       </c>
       <c r="B68" t="n">
-        <v>57953</v>
+        <v>79482</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480781</v>
+        <v>480865</v>
       </c>
       <c r="R68" t="n">
-        <v>6787572</v>
+        <v>6787904</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8027,27 +8025,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Hackmärken färska i gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8062,75 +8055,65 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125106308</t>
+          <t>https://artportalen.se/Sighting/137092052</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112923064</v>
+        <v>137092053</v>
       </c>
       <c r="B69" t="n">
-        <v>58114</v>
+        <v>79482</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480817</v>
+        <v>480874</v>
       </c>
       <c r="R69" t="n">
-        <v>6787576</v>
+        <v>6787824</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8154,22 +8137,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>med apotecier.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8184,69 +8172,65 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923064</t>
+          <t>https://artportalen.se/Sighting/137092053</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112982228</v>
+        <v>137092054</v>
       </c>
       <c r="B70" t="n">
-        <v>58114</v>
+        <v>79482</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480787</v>
+        <v>480890</v>
       </c>
       <c r="R70" t="n">
-        <v>6787755</v>
+        <v>6787756</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8270,22 +8254,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8300,71 +8284,65 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112982228</t>
+          <t>https://artportalen.se/Sighting/137092054</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112923140</v>
+        <v>137092055</v>
       </c>
       <c r="B71" t="n">
-        <v>8455</v>
+        <v>79482</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480817</v>
+        <v>480953</v>
       </c>
       <c r="R71" t="n">
-        <v>6787576</v>
+        <v>6787632</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8388,22 +8366,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8418,71 +8396,65 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923140</t>
+          <t>https://artportalen.se/Sighting/137092055</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112923512</v>
+        <v>137092057</v>
       </c>
       <c r="B72" t="n">
-        <v>8455</v>
+        <v>79482</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480733</v>
+        <v>480994</v>
       </c>
       <c r="R72" t="n">
-        <v>6787668</v>
+        <v>6787648</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8506,22 +8478,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8536,66 +8508,65 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112923512</t>
+          <t>https://artportalen.se/Sighting/137092057</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>112924028</v>
+        <v>112996022</v>
       </c>
       <c r="B73" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>481017</v>
+        <v>480891</v>
       </c>
       <c r="R73" t="n">
-        <v>6787651</v>
+        <v>6787557</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8619,22 +8590,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8649,66 +8610,71 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924028</t>
+          <t>https://artportalen.se/Sighting/112996022</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112924151</v>
+        <v>112924074</v>
       </c>
       <c r="B74" t="n">
-        <v>8455</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Unnån, Unnån, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480927</v>
+        <v>481017</v>
       </c>
       <c r="R74" t="n">
-        <v>6787699</v>
+        <v>6787651</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8737,7 +8703,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8747,7 +8713,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8773,59 +8739,60 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112924151</t>
+          <t>https://artportalen.se/Sighting/112924074</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120747281</v>
+        <v>112980896</v>
       </c>
       <c r="B75" t="n">
-        <v>8455</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480845</v>
+        <v>480919</v>
       </c>
       <c r="R75" t="n">
-        <v>6787659</v>
+        <v>6787525</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8849,17 +8816,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8868,77 +8840,71 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747281</t>
+          <t>https://artportalen.se/Sighting/112980896</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120747340</v>
+        <v>125106308</v>
       </c>
       <c r="B76" t="n">
-        <v>8455</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ekentjärnskogen, Dlr</t>
+          <t>Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480847</v>
+        <v>480781</v>
       </c>
       <c r="R76" t="n">
-        <v>6787707</v>
+        <v>6787572</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8962,17 +8928,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Gnagspår på tallåga</t>
+          <t>Hackmärken färska i gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8981,7 +8957,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8999,59 +8974,64 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747340</t>
+          <t>https://artportalen.se/Sighting/125106308</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135708300</v>
+        <v>112923064</v>
       </c>
       <c r="B77" t="n">
-        <v>8463</v>
+        <v>58114</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ekentjärn, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480839</v>
+        <v>480817</v>
       </c>
       <c r="R77" t="n">
-        <v>6787636</v>
+        <v>6787576</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9075,22 +9055,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9101,91 +9081,73 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708300</t>
+          <t>https://artportalen.se/Sighting/112923064</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119568643</v>
+        <v>112982228</v>
       </c>
       <c r="B78" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>481007</v>
+        <v>480787</v>
       </c>
       <c r="R78" t="n">
-        <v>6787620</v>
+        <v>6787755</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9209,12 +9171,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9223,7 +9195,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9235,22 +9206,22 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568643</t>
+          <t>https://artportalen.se/Sighting/112982228</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125187193</v>
+        <v>112923140</v>
       </c>
       <c r="B79" t="n">
-        <v>104628</v>
+        <v>8455</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9258,43 +9229,40 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222412</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480717</v>
+        <v>480817</v>
       </c>
       <c r="R79" t="n">
-        <v>6787597</v>
+        <v>6787576</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9321,12 +9289,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9352,51 +9330,57 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125187193</t>
+          <t>https://artportalen.se/Sighting/112923140</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112996021</v>
+        <v>112923512</v>
       </c>
       <c r="B80" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480899</v>
+        <v>480733</v>
       </c>
       <c r="R80" t="n">
-        <v>6787538</v>
+        <v>6787668</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9423,12 +9407,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9443,65 +9437,66 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996021</t>
+          <t>https://artportalen.se/Sighting/112923512</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121972913</v>
+        <v>112924028</v>
       </c>
       <c r="B81" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480935</v>
+        <v>481017</v>
       </c>
       <c r="R81" t="n">
-        <v>6787807</v>
+        <v>6787651</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9525,12 +9520,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9545,72 +9550,66 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972913</t>
+          <t>https://artportalen.se/Sighting/112924028</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119568677</v>
+        <v>112924151</v>
       </c>
       <c r="B82" t="n">
-        <v>91402</v>
+        <v>8455</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>256703</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Unnån, Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480971</v>
+        <v>480927</v>
       </c>
       <c r="R82" t="n">
-        <v>6787547</v>
+        <v>6787699</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9634,12 +9633,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9648,7 +9657,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9660,49 +9668,51 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119568677</t>
+          <t>https://artportalen.se/Sighting/112924151</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120747144</v>
+        <v>120747281</v>
       </c>
       <c r="B83" t="n">
-        <v>79350</v>
+        <v>8455</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>260591</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9710,10 +9720,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480904</v>
+        <v>480845</v>
       </c>
       <c r="R83" t="n">
-        <v>6787507</v>
+        <v>6787659</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9750,7 +9760,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9777,43 +9787,45 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747144</t>
+          <t>https://artportalen.se/Sighting/120747281</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120747368</v>
+        <v>120747340</v>
       </c>
       <c r="B84" t="n">
-        <v>79350</v>
+        <v>8455</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>260591</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9821,10 +9833,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480840</v>
+        <v>480847</v>
       </c>
       <c r="R84" t="n">
-        <v>6787710</v>
+        <v>6787707</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9861,7 +9873,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>på tall</t>
+          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9888,51 +9900,56 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120747368</t>
+          <t>https://artportalen.se/Sighting/120747340</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125105944</v>
+        <v>135708300</v>
       </c>
       <c r="B85" t="n">
-        <v>79350</v>
+        <v>8463</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>260591</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481003</v>
+        <v>480839</v>
       </c>
       <c r="R85" t="n">
-        <v>6787803</v>
+        <v>6787636</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9959,22 +9976,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9985,6 +10002,16 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10000,51 +10027,63 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125105944</t>
+          <t>https://artportalen.se/Sighting/135708300</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135710473</v>
+        <v>119568643</v>
       </c>
       <c r="B86" t="n">
-        <v>79477</v>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ekentjärn, Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>480848</v>
+        <v>481007</v>
       </c>
       <c r="R86" t="n">
-        <v>6787635</v>
+        <v>6787620</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10071,27 +10110,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10100,71 +10124,78 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710473</t>
+          <t>https://artportalen.se/Sighting/119568643</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112989992</v>
+        <v>125187193</v>
       </c>
       <c r="B87" t="n">
-        <v>79359</v>
+        <v>104628</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>222412</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>V Ekentjärn, Dlr</t>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481125</v>
+        <v>480717</v>
       </c>
       <c r="R87" t="n">
-        <v>6787708</v>
+        <v>6787597</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10191,17 +10222,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10210,34 +10236,33 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112989992</t>
+          <t>https://artportalen.se/Sighting/125187193</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121972885</v>
+        <v>112996021</v>
       </c>
       <c r="B88" t="n">
-        <v>91909</v>
+        <v>79085</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10245,21 +10270,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10269,10 +10294,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481124</v>
+        <v>480899</v>
       </c>
       <c r="R88" t="n">
-        <v>6787703</v>
+        <v>6787538</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10299,12 +10324,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10319,49 +10344,49 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972885</t>
+          <t>https://artportalen.se/Sighting/112996021</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121972895</v>
+        <v>121972913</v>
       </c>
       <c r="B89" t="n">
-        <v>93213</v>
+        <v>79085</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10371,10 +10396,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481073</v>
+        <v>480935</v>
       </c>
       <c r="R89" t="n">
-        <v>6787790</v>
+        <v>6787807</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10432,51 +10457,58 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972895</t>
+          <t>https://artportalen.se/Sighting/121972913</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>112996034</v>
+        <v>119568677</v>
       </c>
       <c r="B90" t="n">
-        <v>92281</v>
+        <v>91402</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2062</v>
+        <v>256703</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481123</v>
+        <v>480971</v>
       </c>
       <c r="R90" t="n">
-        <v>6787706</v>
+        <v>6787547</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10503,12 +10535,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10517,33 +10549,34 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996034</t>
+          <t>https://artportalen.se/Sighting/119568677</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112996037</v>
+        <v>120747144</v>
       </c>
       <c r="B91" t="n">
-        <v>93197</v>
+        <v>79350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10551,48 +10584,40 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>260591</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481143</v>
+        <v>480904</v>
       </c>
       <c r="R91" t="n">
-        <v>6787609</v>
+        <v>6787507</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10616,12 +10641,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10637,27 +10667,27 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996037</t>
+          <t>https://artportalen.se/Sighting/120747144</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112996031</v>
+        <v>120747368</v>
       </c>
       <c r="B92" t="n">
-        <v>93209</v>
+        <v>79350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10665,48 +10695,40 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4366</v>
+        <v>260591</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnskogen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>481063</v>
+        <v>480840</v>
       </c>
       <c r="R92" t="n">
-        <v>6787744</v>
+        <v>6787710</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10730,12 +10752,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10744,33 +10771,34 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996031</t>
+          <t>https://artportalen.se/Sighting/120747368</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>112990060</v>
+        <v>125105944</v>
       </c>
       <c r="B93" t="n">
-        <v>91930</v>
+        <v>79350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10778,37 +10806,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5442</v>
+        <v>260591</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>481141</v>
+        <v>481003</v>
       </c>
       <c r="R93" t="n">
-        <v>6787582</v>
+        <v>6787803</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10835,17 +10860,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10854,7 +10884,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10866,60 +10895,60 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112990060</t>
+          <t>https://artportalen.se/Sighting/125105944</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>112996032</v>
+        <v>135710473</v>
       </c>
       <c r="B94" t="n">
-        <v>91282</v>
+        <v>79477</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5685</v>
+        <v>260591</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>Ekentjärn, Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>481080</v>
+        <v>480848</v>
       </c>
       <c r="R94" t="n">
-        <v>6787730</v>
+        <v>6787635</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10943,12 +10972,27 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10963,49 +11007,49 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996032</t>
+          <t>https://artportalen.se/Sighting/135710473</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>112996036</v>
+        <v>137092056</v>
       </c>
       <c r="B95" t="n">
-        <v>79327</v>
+        <v>79505</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>260591</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11015,10 +11059,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481143</v>
+        <v>480952</v>
       </c>
       <c r="R95" t="n">
-        <v>6787598</v>
+        <v>6787636</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11045,12 +11089,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11065,27 +11119,27 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996036</t>
+          <t>https://artportalen.se/Sighting/137092056</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>112983277</v>
+        <v>112989992</v>
       </c>
       <c r="B96" t="n">
-        <v>57953</v>
+        <v>79359</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11093,42 +11147,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>481142</v>
+        <v>481125</v>
       </c>
       <c r="R96" t="n">
-        <v>6787700</v>
+        <v>6787708</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11158,19 +11207,14 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:20</t>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11179,73 +11223,69 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+          <t>Irina Röjås, Agnes Rengren, Anton Björk, Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983277</t>
+          <t>https://artportalen.se/Sighting/112989992</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112983978</v>
+        <v>121972885</v>
       </c>
       <c r="B97" t="n">
-        <v>5179</v>
+        <v>91909</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>481104</v>
+        <v>481124</v>
       </c>
       <c r="R97" t="n">
-        <v>6787672</v>
+        <v>6787703</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11272,22 +11312,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11296,81 +11326,71 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983978</t>
+          <t>https://artportalen.se/Sighting/121972885</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>112996035</v>
+        <v>121972895</v>
       </c>
       <c r="B98" t="n">
-        <v>5179</v>
+        <v>93213</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100526</v>
+        <v>2059</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>481128</v>
+        <v>481073</v>
       </c>
       <c r="R98" t="n">
-        <v>6787712</v>
+        <v>6787790</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11394,12 +11414,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11408,56 +11428,55 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Maria Hindemo, Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112996035</t>
+          <t>https://artportalen.se/Sighting/121972895</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121972923</v>
+        <v>112996034</v>
       </c>
       <c r="B99" t="n">
-        <v>5179</v>
+        <v>92281</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100526</v>
+        <v>2062</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11467,10 +11486,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>481148</v>
+        <v>481123</v>
       </c>
       <c r="R99" t="n">
-        <v>6787700</v>
+        <v>6787706</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11497,12 +11516,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11517,65 +11536,76 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972923</t>
+          <t>https://artportalen.se/Sighting/112996034</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121972882</v>
+        <v>112996037</v>
       </c>
       <c r="B100" t="n">
-        <v>5199</v>
+        <v>93197</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>481148</v>
+        <v>481143</v>
       </c>
       <c r="R100" t="n">
-        <v>6787700</v>
+        <v>6787609</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11599,12 +11629,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11613,76 +11643,83 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Maria Hindemo, Maria Blomkvist</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121972882</t>
+          <t>https://artportalen.se/Sighting/112996037</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>112983991</v>
+        <v>112996031</v>
       </c>
       <c r="B101" t="n">
-        <v>8455</v>
+        <v>93209</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+          <t>Ekentjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>481104</v>
+        <v>481063</v>
       </c>
       <c r="R101" t="n">
-        <v>6787672</v>
+        <v>6787744</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11709,55 +11746,44 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112983991</t>
+          <t>https://artportalen.se/Sighting/112996031</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>112996033</v>
+        <v>112990060</v>
       </c>
       <c r="B102" t="n">
-        <v>79085</v>
+        <v>91930</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11765,37 +11791,40 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ekentjärnarna, Dlr</t>
+          <t>V Ekentjärn, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>481079</v>
+        <v>481141</v>
       </c>
       <c r="R102" t="n">
-        <v>6787734</v>
+        <v>6787582</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11827,28 +11856,1572 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Anton Björk, Agnes Rengren, Irina Röjås</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112990060</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>112996032</v>
+      </c>
+      <c r="B103" t="n">
+        <v>91282</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>481080</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6787730</v>
+      </c>
+      <c r="S103" t="n">
+        <v>25</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996032</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>112996036</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>481143</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6787598</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996036</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>137092059</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>481049</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6787643</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137092059</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>137092062</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>481081</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6787664</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137092062</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>137092064</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>481137</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6787697</v>
+      </c>
+      <c r="S107" t="n">
+        <v>8</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137092064</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>137092065</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>481123</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6787703</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137092065</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>137092067</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>481059</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6787716</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137092067</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>112983277</v>
+      </c>
+      <c r="B110" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>481142</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6787700</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Agnes Rengren, Anton Björk, Birgitta Kvist, Irina Röjås, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983277</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>112983978</v>
+      </c>
+      <c r="B111" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>481104</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6787672</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983978</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>112996035</v>
+      </c>
+      <c r="B112" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>481128</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6787712</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112996035</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>121972923</v>
+      </c>
+      <c r="B113" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>481148</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6787700</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972923</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>121972882</v>
+      </c>
+      <c r="B114" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>481148</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6787700</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121972882</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>112983991</v>
+      </c>
+      <c r="B115" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>481104</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6787672</v>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Agnes Rengren, Anton Björk, Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983991</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>112996033</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Ekentjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>481079</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6787734</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Anton Björk, Bengt Oldhammer, Birgitta Kvist, Peter Turander, Irina Röjås, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112996033</t>
         </is>
@@ -11957,6 +13530,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136854171</v>
       </c>
       <c r="B15" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136457415</v>
       </c>
       <c r="B21" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136489706</v>
       </c>
       <c r="B46" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136489707</v>
       </c>
       <c r="B47" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>137092068</v>
       </c>
       <c r="B49" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>136854286</v>
       </c>
       <c r="B64" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>136858154</v>
       </c>
       <c r="B65" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137092050</v>
       </c>
       <c r="B66" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>137092051</v>
       </c>
       <c r="B67" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>137092052</v>
       </c>
       <c r="B68" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>137092053</v>
       </c>
       <c r="B69" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>137092054</v>
       </c>
       <c r="B70" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>137092055</v>
       </c>
       <c r="B71" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>137092057</v>
       </c>
       <c r="B72" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>137092056</v>
       </c>
       <c r="B95" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>137092059</v>
       </c>
       <c r="B105" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>137092062</v>
       </c>
       <c r="B106" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>137092064</v>
       </c>
       <c r="B107" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>137092065</v>
       </c>
       <c r="B108" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>137092067</v>
       </c>
       <c r="B109" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -2131,7 +2131,7 @@
         <v>136854171</v>
       </c>
       <c r="B15" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136457415</v>
       </c>
       <c r="B21" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136489706</v>
       </c>
       <c r="B46" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136489707</v>
       </c>
       <c r="B47" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>137092068</v>
       </c>
       <c r="B49" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136854171</v>
       </c>
       <c r="B15" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136489706</v>
       </c>
       <c r="B46" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136489707</v>
       </c>
       <c r="B47" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>137092068</v>
       </c>
       <c r="B49" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>136854286</v>
       </c>
       <c r="B64" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>136858154</v>
       </c>
       <c r="B65" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137092050</v>
       </c>
       <c r="B66" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>137092051</v>
       </c>
       <c r="B67" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>137092052</v>
       </c>
       <c r="B68" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>137092053</v>
       </c>
       <c r="B69" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>137092054</v>
       </c>
       <c r="B70" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>137092055</v>
       </c>
       <c r="B71" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>137092057</v>
       </c>
       <c r="B72" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>137092056</v>
       </c>
       <c r="B95" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>137092059</v>
       </c>
       <c r="B105" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>137092062</v>
       </c>
       <c r="B106" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>137092064</v>
       </c>
       <c r="B107" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>137092065</v>
       </c>
       <c r="B108" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>137092067</v>
       </c>
       <c r="B109" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136854171</v>
       </c>
       <c r="B15" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>137092068</v>
       </c>
       <c r="B49" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>136854286</v>
       </c>
       <c r="B64" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>136858154</v>
       </c>
       <c r="B65" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137092050</v>
       </c>
       <c r="B66" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>137092051</v>
       </c>
       <c r="B67" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>137092052</v>
       </c>
       <c r="B68" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>137092053</v>
       </c>
       <c r="B69" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>137092054</v>
       </c>
       <c r="B70" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>137092055</v>
       </c>
       <c r="B71" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>137092057</v>
       </c>
       <c r="B72" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>137092056</v>
       </c>
       <c r="B95" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>137092059</v>
       </c>
       <c r="B105" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>137092062</v>
       </c>
       <c r="B106" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>137092064</v>
       </c>
       <c r="B107" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>137092065</v>
       </c>
       <c r="B108" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>137092067</v>
       </c>
       <c r="B109" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136854171</v>
       </c>
       <c r="B15" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>137092068</v>
       </c>
       <c r="B49" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>136854286</v>
       </c>
       <c r="B64" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>136858154</v>
       </c>
       <c r="B65" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137092050</v>
       </c>
       <c r="B66" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>137092051</v>
       </c>
       <c r="B67" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>137092052</v>
       </c>
       <c r="B68" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>137092053</v>
       </c>
       <c r="B69" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>137092054</v>
       </c>
       <c r="B70" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>137092055</v>
       </c>
       <c r="B71" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>137092057</v>
       </c>
       <c r="B72" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>137092056</v>
       </c>
       <c r="B95" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>137092059</v>
       </c>
       <c r="B105" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>137092062</v>
       </c>
       <c r="B106" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>137092064</v>
       </c>
       <c r="B107" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>137092065</v>
       </c>
       <c r="B108" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>137092067</v>
       </c>
       <c r="B109" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136854171</v>
       </c>
       <c r="B15" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>137092068</v>
       </c>
       <c r="B49" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>136854286</v>
       </c>
       <c r="B64" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>136858154</v>
       </c>
       <c r="B65" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137092050</v>
       </c>
       <c r="B66" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>137092051</v>
       </c>
       <c r="B67" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>137092052</v>
       </c>
       <c r="B68" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>137092053</v>
       </c>
       <c r="B69" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>137092054</v>
       </c>
       <c r="B70" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>137092055</v>
       </c>
       <c r="B71" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>137092057</v>
       </c>
       <c r="B72" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>137092056</v>
       </c>
       <c r="B95" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>137092059</v>
       </c>
       <c r="B105" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>137092062</v>
       </c>
       <c r="B106" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>137092064</v>
       </c>
       <c r="B107" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>137092065</v>
       </c>
       <c r="B108" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>137092067</v>
       </c>
       <c r="B109" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -2131,7 +2131,7 @@
         <v>136854171</v>
       </c>
       <c r="B15" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>137092068</v>
       </c>
       <c r="B49" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1813,7 +1813,7 @@
         <v>137300892</v>
       </c>
       <c r="B12" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137300235</v>
       </c>
       <c r="B16" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137300906</v>
       </c>
       <c r="B17" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136854171</v>
       </c>
       <c r="B19" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>137092068</v>
       </c>
       <c r="B53" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10841,7 +10841,7 @@
         <v>137300085</v>
       </c>
       <c r="B93" t="n">
-        <v>108512</v>
+        <v>108513</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137299536</v>
       </c>
       <c r="B10" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>137300892</v>
       </c>
       <c r="B12" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137300235</v>
       </c>
       <c r="B16" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137300906</v>
       </c>
       <c r="B17" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136854171</v>
       </c>
       <c r="B19" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>137092068</v>
       </c>
       <c r="B53" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>136854286</v>
       </c>
       <c r="B68" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>136858154</v>
       </c>
       <c r="B69" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>137092050</v>
       </c>
       <c r="B70" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>137092051</v>
       </c>
       <c r="B71" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>137092052</v>
       </c>
       <c r="B72" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>137092053</v>
       </c>
       <c r="B73" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>137092054</v>
       </c>
       <c r="B74" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>137092055</v>
       </c>
       <c r="B75" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>137092057</v>
       </c>
       <c r="B76" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>137300005</v>
       </c>
       <c r="B81" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
         <v>137301380</v>
       </c>
       <c r="B84" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10841,7 +10841,7 @@
         <v>137300085</v>
       </c>
       <c r="B93" t="n">
-        <v>108513</v>
+        <v>108518</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>137092056</v>
       </c>
       <c r="B103" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>137092059</v>
       </c>
       <c r="B113" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>137092062</v>
       </c>
       <c r="B114" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>137092064</v>
       </c>
       <c r="B115" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>137092065</v>
       </c>
       <c r="B116" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>137092067</v>
       </c>
       <c r="B117" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1813,7 +1813,7 @@
         <v>137300892</v>
       </c>
       <c r="B12" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2256,7 +2256,7 @@
         <v>137300235</v>
       </c>
       <c r="B16" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137300906</v>
       </c>
       <c r="B17" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
         <v>136854171</v>
       </c>
       <c r="B19" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>137092068</v>
       </c>
       <c r="B53" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10841,7 +10841,7 @@
         <v>137300085</v>
       </c>
       <c r="B93" t="n">
-        <v>108518</v>
+        <v>108521</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137299536</v>
       </c>
       <c r="B10" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>137300892</v>
       </c>
       <c r="B12" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2256,7 +2256,7 @@
         <v>137300235</v>
       </c>
       <c r="B16" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137300906</v>
       </c>
       <c r="B17" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
         <v>136854171</v>
       </c>
       <c r="B19" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>137092068</v>
       </c>
       <c r="B53" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>136854286</v>
       </c>
       <c r="B68" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>136858154</v>
       </c>
       <c r="B69" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>137092050</v>
       </c>
       <c r="B70" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>137092051</v>
       </c>
       <c r="B71" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>137092052</v>
       </c>
       <c r="B72" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>137092053</v>
       </c>
       <c r="B73" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>137092054</v>
       </c>
       <c r="B74" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>137092055</v>
       </c>
       <c r="B75" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>137092057</v>
       </c>
       <c r="B76" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>137300005</v>
       </c>
       <c r="B81" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
         <v>137301380</v>
       </c>
       <c r="B84" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>137300085</v>
       </c>
       <c r="B93" t="n">
-        <v>108521</v>
+        <v>108527</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>137092056</v>
       </c>
       <c r="B103" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>137092059</v>
       </c>
       <c r="B113" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>137092062</v>
       </c>
       <c r="B114" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>137092064</v>
       </c>
       <c r="B115" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>137092065</v>
       </c>
       <c r="B116" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>137092067</v>
       </c>
       <c r="B117" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10841,7 +10841,7 @@
         <v>137300085</v>
       </c>
       <c r="B93" t="n">
-        <v>108527</v>
+        <v>108528</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137299536</v>
       </c>
       <c r="B10" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>137300892</v>
       </c>
       <c r="B12" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137300235</v>
       </c>
       <c r="B16" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137300906</v>
       </c>
       <c r="B17" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136854171</v>
       </c>
       <c r="B19" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>137092068</v>
       </c>
       <c r="B53" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>136854286</v>
       </c>
       <c r="B68" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>136858154</v>
       </c>
       <c r="B69" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>137092050</v>
       </c>
       <c r="B70" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>137092051</v>
       </c>
       <c r="B71" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>137092052</v>
       </c>
       <c r="B72" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>137092053</v>
       </c>
       <c r="B73" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>137092054</v>
       </c>
       <c r="B74" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>137092055</v>
       </c>
       <c r="B75" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>137092057</v>
       </c>
       <c r="B76" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10841,7 +10841,7 @@
         <v>137300085</v>
       </c>
       <c r="B93" t="n">
-        <v>108528</v>
+        <v>108540</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>137092056</v>
       </c>
       <c r="B103" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>137092059</v>
       </c>
       <c r="B113" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>137092062</v>
       </c>
       <c r="B114" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>137092064</v>
       </c>
       <c r="B115" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>137092065</v>
       </c>
       <c r="B116" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>137092067</v>
       </c>
       <c r="B117" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137299536</v>
       </c>
       <c r="B10" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>137300892</v>
       </c>
       <c r="B12" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137300235</v>
       </c>
       <c r="B16" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137300906</v>
       </c>
       <c r="B17" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>137092068</v>
       </c>
       <c r="B53" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>136854286</v>
       </c>
       <c r="B68" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>137092050</v>
       </c>
       <c r="B70" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>137092051</v>
       </c>
       <c r="B71" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>137092052</v>
       </c>
       <c r="B72" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>137092053</v>
       </c>
       <c r="B73" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>137092054</v>
       </c>
       <c r="B74" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>137092055</v>
       </c>
       <c r="B75" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>137092057</v>
       </c>
       <c r="B76" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10841,7 +10841,7 @@
         <v>137300085</v>
       </c>
       <c r="B93" t="n">
-        <v>108540</v>
+        <v>108541</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>137092056</v>
       </c>
       <c r="B103" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>137092059</v>
       </c>
       <c r="B113" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>137092062</v>
       </c>
       <c r="B114" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>137092064</v>
       </c>
       <c r="B115" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>137092065</v>
       </c>
       <c r="B116" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>137092067</v>
       </c>
       <c r="B117" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137299536</v>
       </c>
       <c r="B10" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>137300892</v>
       </c>
       <c r="B12" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137300235</v>
       </c>
       <c r="B16" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137300906</v>
       </c>
       <c r="B17" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>137092068</v>
       </c>
       <c r="B53" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>136854286</v>
       </c>
       <c r="B68" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>137092050</v>
       </c>
       <c r="B70" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>137092051</v>
       </c>
       <c r="B71" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>137092052</v>
       </c>
       <c r="B72" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>137092053</v>
       </c>
       <c r="B73" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>137092054</v>
       </c>
       <c r="B74" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>137092055</v>
       </c>
       <c r="B75" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>137092057</v>
       </c>
       <c r="B76" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>137300085</v>
       </c>
       <c r="B93" t="n">
-        <v>108541</v>
+        <v>108544</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>137092056</v>
       </c>
       <c r="B103" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>137092059</v>
       </c>
       <c r="B113" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>137092062</v>
       </c>
       <c r="B114" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>137092064</v>
       </c>
       <c r="B115" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>137092065</v>
       </c>
       <c r="B116" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>137092067</v>
       </c>
       <c r="B117" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10938,7 +10938,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79567</v>
+        <v>79568</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>136854286</v>
       </c>
       <c r="B68" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 45776-2023 artfynd.xlsx
+++ b/artfynd/A 45776-2023 artfynd.xlsx
@@ -1478,7 +1478,7 @@
         <v>136854283</v>
       </c>
       <c r="B9" t="n">
-        <v>79568</v>
+        <v>79571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137299536</v>
       </c>
       <c r="B10" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>137300892</v>
       </c>
       <c r="B12" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137300235</v>
       </c>
       <c r="B16" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137300906</v>
       </c>
       <c r="B17" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>137092068</v>
       </c>
       <c r="B53" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>136854286</v>
       </c>
       <c r="B68" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>137092050</v>
       </c>
       <c r="B70" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>137092051</v>
       </c>
       <c r="B71" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>137092052</v>
       </c>
       <c r="B72" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>137092053</v>
       </c>
       <c r="B73" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>137092054</v>
       </c>
       <c r="B74" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>137092055</v>
       </c>
       <c r="B75" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>137092057</v>
       </c>
       <c r="B76" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>137300005</v>
       </c>
       <c r="B81" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>137301380</v>
       </c>
       <c r="B84" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10841,7 +10841,7 @@
         <v>137300085</v>
       </c>
       <c r="B93" t="n">
-        <v>108544</v>
+        <v>108550</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11944,7 +11944,7 @@
         <v>137092056</v>
       </c>
       <c r="B103" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>137092059</v>
       </c>
       <c r="B113" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>137092062</v>
       </c>
       <c r="B114" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>137092064</v>
       </c>
       <c r="B115" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>137092065</v>
       </c>
       <c r="B116" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>137092067</v>
       </c>
       <c r="B117" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
